--- a/input/2026H1门店经营台账.xlsx
+++ b/input/2026H1门店经营台账.xlsx
@@ -2858,13 +2858,13 @@
         <v>0.266</v>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L2" t="n">
         <v>7</v>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" t="n">
         <v>7479.49</v>
@@ -2885,7 +2885,7 @@
         <v>0.0172</v>
       </c>
       <c r="T2" t="n">
-        <v>19138.32</v>
+        <v>17868.01</v>
       </c>
     </row>
     <row r="3">
@@ -2924,13 +2924,13 @@
         <v>0.4281</v>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
         <v>23572.11</v>
@@ -2951,7 +2951,7 @@
         <v>0.0492</v>
       </c>
       <c r="T3" t="n">
-        <v>17683.83</v>
+        <v>22101.88</v>
       </c>
     </row>
     <row r="4">
@@ -3017,7 +3017,7 @@
         <v>0.0392</v>
       </c>
       <c r="T4" t="n">
-        <v>18462.64</v>
+        <v>16263</v>
       </c>
     </row>
     <row r="5">
@@ -3056,10 +3056,10 @@
         <v>0.3843</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
         <v>4</v>
@@ -3083,7 +3083,7 @@
         <v>0.03</v>
       </c>
       <c r="T5" t="n">
-        <v>4781.26</v>
+        <v>5639.75</v>
       </c>
     </row>
     <row r="6">
@@ -3122,13 +3122,13 @@
         <v>0.4497</v>
       </c>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
         <v>11125.34</v>
@@ -3149,7 +3149,7 @@
         <v>0.008699999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>10188.58</v>
+        <v>8329.290000000001</v>
       </c>
     </row>
     <row r="7">
@@ -3188,10 +3188,10 @@
         <v>0.4262</v>
       </c>
       <c r="K7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
         <v>5</v>
@@ -3215,7 +3215,7 @@
         <v>0.0151</v>
       </c>
       <c r="T7" t="n">
-        <v>8372.450000000001</v>
+        <v>8425.15</v>
       </c>
     </row>
     <row r="8">
@@ -3254,13 +3254,13 @@
         <v>0.4474</v>
       </c>
       <c r="K8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N8" t="n">
         <v>6828.48</v>
@@ -3281,7 +3281,7 @@
         <v>0.0128</v>
       </c>
       <c r="T8" t="n">
-        <v>12179</v>
+        <v>10522.73</v>
       </c>
     </row>
     <row r="9">
@@ -3320,13 +3320,13 @@
         <v>0.4378</v>
       </c>
       <c r="K9" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N9" t="n">
         <v>4975.58</v>
@@ -3347,7 +3347,7 @@
         <v>0.0391</v>
       </c>
       <c r="T9" t="n">
-        <v>7970.22</v>
+        <v>12368.17</v>
       </c>
     </row>
     <row r="10">
@@ -3386,13 +3386,13 @@
         <v>0.371</v>
       </c>
       <c r="K10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L10" t="n">
         <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N10" t="n">
         <v>9372.889999999999</v>
@@ -3413,7 +3413,7 @@
         <v>0.0095</v>
       </c>
       <c r="T10" t="n">
-        <v>6248.43</v>
+        <v>7842.95</v>
       </c>
     </row>
     <row r="11">
@@ -3452,13 +3452,13 @@
         <v>0.4311</v>
       </c>
       <c r="K11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L11" t="n">
         <v>13</v>
       </c>
       <c r="M11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N11" t="n">
         <v>20639.91</v>
@@ -3479,7 +3479,7 @@
         <v>0.0395</v>
       </c>
       <c r="T11" t="n">
-        <v>19666.14</v>
+        <v>19019.94</v>
       </c>
     </row>
     <row r="12">
@@ -3518,10 +3518,10 @@
         <v>0.4042</v>
       </c>
       <c r="K12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
         <v>6</v>
@@ -3545,7 +3545,7 @@
         <v>0.0251</v>
       </c>
       <c r="T12" t="n">
-        <v>13071.5</v>
+        <v>8997.43</v>
       </c>
     </row>
     <row r="13">
@@ -3584,13 +3584,13 @@
         <v>0.2519</v>
       </c>
       <c r="K13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L13" t="n">
         <v>4</v>
       </c>
       <c r="M13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
         <v>21871.59</v>
@@ -3611,7 +3611,7 @@
         <v>0.0443</v>
       </c>
       <c r="T13" t="n">
-        <v>7715.86</v>
+        <v>8099.93</v>
       </c>
     </row>
     <row r="14">
@@ -3653,10 +3653,10 @@
         <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
         <v>35204.37</v>
@@ -3677,7 +3677,7 @@
         <v>0.0059</v>
       </c>
       <c r="T14" t="n">
-        <v>1493.29</v>
+        <v>2144.22</v>
       </c>
     </row>
     <row r="15">
@@ -3716,13 +3716,13 @@
         <v>0.4298</v>
       </c>
       <c r="K15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N15" t="n">
         <v>33639.03</v>
@@ -3743,7 +3743,7 @@
         <v>0.0303</v>
       </c>
       <c r="T15" t="n">
-        <v>21950.51</v>
+        <v>21673.44</v>
       </c>
     </row>
     <row r="16">
@@ -3782,13 +3782,13 @@
         <v>0.3313</v>
       </c>
       <c r="K16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L16" t="n">
         <v>7</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
         <v>25814.66</v>
@@ -3809,7 +3809,7 @@
         <v>0.0364</v>
       </c>
       <c r="T16" t="n">
-        <v>5241.64</v>
+        <v>9900.129999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3851,10 +3851,10 @@
         <v>16</v>
       </c>
       <c r="L17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
         <v>9183.860000000001</v>
@@ -3875,7 +3875,7 @@
         <v>0.0301</v>
       </c>
       <c r="T17" t="n">
-        <v>11645.64</v>
+        <v>10368.24</v>
       </c>
     </row>
     <row r="18">
@@ -3914,10 +3914,10 @@
         <v>0.4104</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
         <v>3</v>
@@ -3941,7 +3941,7 @@
         <v>0.0274</v>
       </c>
       <c r="T18" t="n">
-        <v>3103.32</v>
+        <v>2418.16</v>
       </c>
     </row>
     <row r="19">
@@ -3980,13 +3980,13 @@
         <v>0.4244</v>
       </c>
       <c r="K19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N19" t="n">
         <v>41614.85</v>
@@ -4007,7 +4007,7 @@
         <v>0.0072</v>
       </c>
       <c r="T19" t="n">
-        <v>10546.77</v>
+        <v>7476.98</v>
       </c>
     </row>
     <row r="20">
@@ -4046,10 +4046,10 @@
         <v>0.2955</v>
       </c>
       <c r="K20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M20" t="n">
         <v>10</v>
@@ -4073,7 +4073,7 @@
         <v>0.0279</v>
       </c>
       <c r="T20" t="n">
-        <v>9325.6</v>
+        <v>7099.66</v>
       </c>
     </row>
     <row r="21">
@@ -4112,13 +4112,13 @@
         <v>0.3058</v>
       </c>
       <c r="K21" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L21" t="n">
         <v>7</v>
       </c>
       <c r="M21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N21" t="n">
         <v>11621.99</v>
@@ -4139,7 +4139,7 @@
         <v>0.0228</v>
       </c>
       <c r="T21" t="n">
-        <v>10682.66</v>
+        <v>14396.59</v>
       </c>
     </row>
     <row r="22">
@@ -4178,13 +4178,13 @@
         <v>0.2731</v>
       </c>
       <c r="K22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N22" t="n">
         <v>15844.72</v>
@@ -4205,7 +4205,7 @@
         <v>0.0251</v>
       </c>
       <c r="T22" t="n">
-        <v>18351.04</v>
+        <v>21558.91</v>
       </c>
     </row>
     <row r="23">
@@ -4244,13 +4244,13 @@
         <v>0.3369</v>
       </c>
       <c r="K23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
         <v>8140.58</v>
@@ -4271,7 +4271,7 @@
         <v>0.021</v>
       </c>
       <c r="T23" t="n">
-        <v>3131.8</v>
+        <v>2612.8</v>
       </c>
     </row>
     <row r="24">
@@ -4310,13 +4310,13 @@
         <v>0.3653</v>
       </c>
       <c r="K24" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N24" t="n">
         <v>4709.83</v>
@@ -4337,7 +4337,7 @@
         <v>0.0354</v>
       </c>
       <c r="T24" t="n">
-        <v>35598.4</v>
+        <v>31249.74</v>
       </c>
     </row>
     <row r="25">
@@ -4376,10 +4376,10 @@
         <v>0.3939</v>
       </c>
       <c r="K25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M25" t="n">
         <v>7</v>
@@ -4403,7 +4403,7 @@
         <v>0.0151</v>
       </c>
       <c r="T25" t="n">
-        <v>7456.53</v>
+        <v>7628.33</v>
       </c>
     </row>
     <row r="26">
@@ -4445,10 +4445,10 @@
         <v>9</v>
       </c>
       <c r="L26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M26" t="n">
         <v>5</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4</v>
       </c>
       <c r="N26" t="n">
         <v>14909.22</v>
@@ -4469,7 +4469,7 @@
         <v>0.0417</v>
       </c>
       <c r="T26" t="n">
-        <v>3535.2</v>
+        <v>10601.33</v>
       </c>
     </row>
     <row r="27">
@@ -4508,13 +4508,13 @@
         <v>0.3305</v>
       </c>
       <c r="K27" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="L27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="N27" t="n">
         <v>23228.15</v>
@@ -4535,7 +4535,7 @@
         <v>0.0485</v>
       </c>
       <c r="T27" t="n">
-        <v>10915.29</v>
+        <v>12882.78</v>
       </c>
     </row>
     <row r="28">
@@ -4574,13 +4574,13 @@
         <v>0.4306</v>
       </c>
       <c r="K28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
         <v>18343.43</v>
@@ -4601,7 +4601,7 @@
         <v>0.0186</v>
       </c>
       <c r="T28" t="n">
-        <v>12766.59</v>
+        <v>11663.55</v>
       </c>
     </row>
     <row r="29">
@@ -4640,13 +4640,13 @@
         <v>0.336</v>
       </c>
       <c r="K29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L29" t="n">
         <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N29" t="n">
         <v>14870.82</v>
@@ -4667,7 +4667,7 @@
         <v>0.0443</v>
       </c>
       <c r="T29" t="n">
-        <v>12843.8</v>
+        <v>7169.48</v>
       </c>
     </row>
     <row r="30">
@@ -4706,13 +4706,13 @@
         <v>0.3446</v>
       </c>
       <c r="K30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N30" t="n">
         <v>23741.21</v>
@@ -4733,7 +4733,7 @@
         <v>0.0221</v>
       </c>
       <c r="T30" t="n">
-        <v>6101.82</v>
+        <v>5642.69</v>
       </c>
     </row>
     <row r="31">
@@ -4772,13 +4772,13 @@
         <v>0.3766</v>
       </c>
       <c r="K31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N31" t="n">
         <v>15458.89</v>
@@ -4799,7 +4799,7 @@
         <v>0.0227</v>
       </c>
       <c r="T31" t="n">
-        <v>5905.94</v>
+        <v>4108.81</v>
       </c>
     </row>
     <row r="32">
@@ -4838,13 +4838,13 @@
         <v>0.2549</v>
       </c>
       <c r="K32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L32" t="n">
         <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N32" t="n">
         <v>3499.45</v>
@@ -4865,7 +4865,7 @@
         <v>0.0191</v>
       </c>
       <c r="T32" t="n">
-        <v>15089.11</v>
+        <v>12842.81</v>
       </c>
     </row>
     <row r="33">
@@ -4904,13 +4904,13 @@
         <v>0.376</v>
       </c>
       <c r="K33" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M33" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="N33" t="n">
         <v>15690.73</v>
@@ -4931,7 +4931,7 @@
         <v>0.0256</v>
       </c>
       <c r="T33" t="n">
-        <v>6423.33</v>
+        <v>16116.95</v>
       </c>
     </row>
     <row r="34">
@@ -4970,13 +4970,13 @@
         <v>0.2511</v>
       </c>
       <c r="K34" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M34" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N34" t="n">
         <v>15042.18</v>
@@ -4997,7 +4997,7 @@
         <v>0.0098</v>
       </c>
       <c r="T34" t="n">
-        <v>22088.08</v>
+        <v>19938.32</v>
       </c>
     </row>
     <row r="35">
@@ -5039,10 +5039,10 @@
         <v>10</v>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N35" t="n">
         <v>11018.86</v>
@@ -5063,7 +5063,7 @@
         <v>0.0308</v>
       </c>
       <c r="T35" t="n">
-        <v>14636.41</v>
+        <v>15434.98</v>
       </c>
     </row>
     <row r="36">
@@ -5102,13 +5102,13 @@
         <v>0.4103</v>
       </c>
       <c r="K36" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N36" t="n">
         <v>9793.77</v>
@@ -5129,7 +5129,7 @@
         <v>0.0342</v>
       </c>
       <c r="T36" t="n">
-        <v>11663.66</v>
+        <v>5633.82</v>
       </c>
     </row>
     <row r="37">
@@ -5171,10 +5171,10 @@
         <v>7</v>
       </c>
       <c r="L37" t="n">
+        <v>4</v>
+      </c>
+      <c r="M37" t="n">
         <v>3</v>
-      </c>
-      <c r="M37" t="n">
-        <v>4</v>
       </c>
       <c r="N37" t="n">
         <v>23969.65</v>
@@ -5195,7 +5195,7 @@
         <v>0.0406</v>
       </c>
       <c r="T37" t="n">
-        <v>7240.21</v>
+        <v>7173.92</v>
       </c>
     </row>
     <row r="38">
@@ -5261,7 +5261,7 @@
         <v>0.0194</v>
       </c>
       <c r="T38" t="n">
-        <v>24815.18</v>
+        <v>21219.98</v>
       </c>
     </row>
     <row r="39">
@@ -5300,13 +5300,13 @@
         <v>0.3753</v>
       </c>
       <c r="K39" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N39" t="n">
         <v>18431</v>
@@ -5327,7 +5327,7 @@
         <v>0.0147</v>
       </c>
       <c r="T39" t="n">
-        <v>25889.74</v>
+        <v>23230.86</v>
       </c>
     </row>
     <row r="40">
@@ -5366,13 +5366,13 @@
         <v>0.358</v>
       </c>
       <c r="K40" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N40" t="n">
         <v>8472.24</v>
@@ -5393,7 +5393,7 @@
         <v>0.0242</v>
       </c>
       <c r="T40" t="n">
-        <v>11717.3</v>
+        <v>9001.809999999999</v>
       </c>
     </row>
     <row r="41">
@@ -5432,13 +5432,13 @@
         <v>0.3315</v>
       </c>
       <c r="K41" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L41" t="n">
+        <v>6</v>
+      </c>
+      <c r="M41" t="n">
         <v>7</v>
-      </c>
-      <c r="M41" t="n">
-        <v>9</v>
       </c>
       <c r="N41" t="n">
         <v>8886.66</v>
@@ -5459,7 +5459,7 @@
         <v>0.0209</v>
       </c>
       <c r="T41" t="n">
-        <v>12282.38</v>
+        <v>11866.66</v>
       </c>
     </row>
     <row r="42">
@@ -5498,13 +5498,13 @@
         <v>0.3668</v>
       </c>
       <c r="K42" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L42" t="n">
         <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N42" t="n">
         <v>9548.67</v>
@@ -5525,7 +5525,7 @@
         <v>0.0389</v>
       </c>
       <c r="T42" t="n">
-        <v>6169.72</v>
+        <v>6624.67</v>
       </c>
     </row>
     <row r="43">
@@ -5567,10 +5567,10 @@
         <v>8</v>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
         <v>16924.14</v>
@@ -5591,7 +5591,7 @@
         <v>0.0303</v>
       </c>
       <c r="T43" t="n">
-        <v>2844.87</v>
+        <v>11775.21</v>
       </c>
     </row>
     <row r="44">
@@ -5633,10 +5633,10 @@
         <v>13</v>
       </c>
       <c r="L44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M44" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N44" t="n">
         <v>7235.97</v>
@@ -5657,7 +5657,7 @@
         <v>0.0239</v>
       </c>
       <c r="T44" t="n">
-        <v>20490.94</v>
+        <v>18049.7</v>
       </c>
     </row>
     <row r="45">
@@ -5696,10 +5696,10 @@
         <v>0.3858</v>
       </c>
       <c r="K45" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L45" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M45" t="n">
         <v>8</v>
@@ -5723,7 +5723,7 @@
         <v>0.0316</v>
       </c>
       <c r="T45" t="n">
-        <v>22292.7</v>
+        <v>21591.11</v>
       </c>
     </row>
     <row r="46">
@@ -5762,13 +5762,13 @@
         <v>0.2554</v>
       </c>
       <c r="K46" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L46" t="n">
         <v>7</v>
       </c>
       <c r="M46" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N46" t="n">
         <v>24145.84</v>
@@ -5789,7 +5789,7 @@
         <v>0.0226</v>
       </c>
       <c r="T46" t="n">
-        <v>22216.2</v>
+        <v>30666.25</v>
       </c>
     </row>
     <row r="47">
@@ -5828,13 +5828,13 @@
         <v>0.3423</v>
       </c>
       <c r="K47" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L47" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M47" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
         <v>24661.31</v>
@@ -5855,7 +5855,7 @@
         <v>0.0297</v>
       </c>
       <c r="T47" t="n">
-        <v>6054.7</v>
+        <v>3427.01</v>
       </c>
     </row>
     <row r="48">
@@ -5894,10 +5894,10 @@
         <v>0.3258</v>
       </c>
       <c r="K48" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L48" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M48" t="n">
         <v>12</v>
@@ -5921,7 +5921,7 @@
         <v>0.042</v>
       </c>
       <c r="T48" t="n">
-        <v>16223.18</v>
+        <v>14662.52</v>
       </c>
     </row>
     <row r="49">
@@ -5963,10 +5963,10 @@
         <v>14</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N49" t="n">
         <v>29860.4</v>
@@ -5987,7 +5987,7 @@
         <v>0.0429</v>
       </c>
       <c r="T49" t="n">
-        <v>8965.799999999999</v>
+        <v>7846.93</v>
       </c>
     </row>
     <row r="50">
@@ -6026,10 +6026,10 @@
         <v>0.4399</v>
       </c>
       <c r="K50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M50" t="n">
         <v>11</v>
@@ -6053,7 +6053,7 @@
         <v>0.0113</v>
       </c>
       <c r="T50" t="n">
-        <v>17156.9</v>
+        <v>18080.76</v>
       </c>
     </row>
     <row r="51">
@@ -6092,13 +6092,13 @@
         <v>0.3628</v>
       </c>
       <c r="K51" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N51" t="n">
         <v>5855.63</v>
@@ -6119,7 +6119,7 @@
         <v>0.0429</v>
       </c>
       <c r="T51" t="n">
-        <v>12411.12</v>
+        <v>13095.25</v>
       </c>
     </row>
     <row r="52">
@@ -6158,13 +6158,13 @@
         <v>0.3996</v>
       </c>
       <c r="K52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L52" t="n">
         <v>5</v>
       </c>
       <c r="M52" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N52" t="n">
         <v>4256.84</v>
@@ -6185,7 +6185,7 @@
         <v>0.0245</v>
       </c>
       <c r="T52" t="n">
-        <v>15697.04</v>
+        <v>13390.24</v>
       </c>
     </row>
     <row r="53">
@@ -6224,10 +6224,10 @@
         <v>0.3124</v>
       </c>
       <c r="K53" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M53" t="n">
         <v>9</v>
@@ -6251,7 +6251,7 @@
         <v>0.0244</v>
       </c>
       <c r="T53" t="n">
-        <v>21822.95</v>
+        <v>22336.18</v>
       </c>
     </row>
     <row r="54">
@@ -6290,13 +6290,13 @@
         <v>0.3881</v>
       </c>
       <c r="K54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L54" t="n">
+        <v>3</v>
+      </c>
+      <c r="M54" t="n">
         <v>5</v>
-      </c>
-      <c r="M54" t="n">
-        <v>4</v>
       </c>
       <c r="N54" t="n">
         <v>19579.95</v>
@@ -6317,7 +6317,7 @@
         <v>0.0236</v>
       </c>
       <c r="T54" t="n">
-        <v>11026.12</v>
+        <v>10036.32</v>
       </c>
     </row>
     <row r="55">
@@ -6356,13 +6356,13 @@
         <v>0.2742</v>
       </c>
       <c r="K55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L55" t="n">
         <v>5</v>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
         <v>7970</v>
@@ -6383,7 +6383,7 @@
         <v>0.0466</v>
       </c>
       <c r="T55" t="n">
-        <v>840.79</v>
+        <v>2016.17</v>
       </c>
     </row>
     <row r="56">
@@ -6422,13 +6422,13 @@
         <v>0.3182</v>
       </c>
       <c r="K56" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L56" t="n">
         <v>6</v>
       </c>
       <c r="M56" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N56" t="n">
         <v>19593.29</v>
@@ -6449,7 +6449,7 @@
         <v>0.0404</v>
       </c>
       <c r="T56" t="n">
-        <v>11544.18</v>
+        <v>11628.93</v>
       </c>
     </row>
     <row r="57">
@@ -6488,13 +6488,13 @@
         <v>0.4157</v>
       </c>
       <c r="K57" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N57" t="n">
         <v>24445.83</v>
@@ -6515,7 +6515,7 @@
         <v>0.0098</v>
       </c>
       <c r="T57" t="n">
-        <v>13229.98</v>
+        <v>20027.69</v>
       </c>
     </row>
     <row r="58">
@@ -6557,10 +6557,10 @@
         <v>11</v>
       </c>
       <c r="L58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N58" t="n">
         <v>10003.78</v>
@@ -6581,7 +6581,7 @@
         <v>0.0362</v>
       </c>
       <c r="T58" t="n">
-        <v>3136.45</v>
+        <v>3909.71</v>
       </c>
     </row>
     <row r="59">
@@ -6620,13 +6620,13 @@
         <v>0.4203</v>
       </c>
       <c r="K59" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N59" t="n">
         <v>3951.12</v>
@@ -6647,7 +6647,7 @@
         <v>0.0169</v>
       </c>
       <c r="T59" t="n">
-        <v>14339.54</v>
+        <v>8024.75</v>
       </c>
     </row>
     <row r="60">
@@ -6686,13 +6686,13 @@
         <v>0.3721</v>
       </c>
       <c r="K60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L60" t="n">
         <v>5</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N60" t="n">
         <v>10557.46</v>
@@ -6713,7 +6713,7 @@
         <v>0.008200000000000001</v>
       </c>
       <c r="T60" t="n">
-        <v>4159.25</v>
+        <v>1113.02</v>
       </c>
     </row>
     <row r="61">
@@ -6752,10 +6752,10 @@
         <v>0.4096</v>
       </c>
       <c r="K61" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M61" t="n">
         <v>8</v>
@@ -6779,7 +6779,7 @@
         <v>0.0382</v>
       </c>
       <c r="T61" t="n">
-        <v>21209.64</v>
+        <v>22914.94</v>
       </c>
     </row>
     <row r="62">
@@ -6818,10 +6818,10 @@
         <v>0.2671</v>
       </c>
       <c r="K62" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M62" t="n">
         <v>5</v>
@@ -6845,7 +6845,7 @@
         <v>0.0491</v>
       </c>
       <c r="T62" t="n">
-        <v>10300.85</v>
+        <v>7950.02</v>
       </c>
     </row>
     <row r="63">
@@ -6884,13 +6884,13 @@
         <v>0.3482</v>
       </c>
       <c r="K63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L63" t="n">
         <v>5</v>
       </c>
       <c r="M63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N63" t="n">
         <v>19187.4</v>
@@ -6911,7 +6911,7 @@
         <v>0.0444</v>
       </c>
       <c r="T63" t="n">
-        <v>3705.63</v>
+        <v>6702.51</v>
       </c>
     </row>
     <row r="64">
@@ -6950,13 +6950,13 @@
         <v>0.3663</v>
       </c>
       <c r="K64" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L64" t="n">
         <v>7</v>
       </c>
       <c r="M64" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N64" t="n">
         <v>13344.71</v>
@@ -6977,7 +6977,7 @@
         <v>0.0431</v>
       </c>
       <c r="T64" t="n">
-        <v>16210.78</v>
+        <v>12564.85</v>
       </c>
     </row>
     <row r="65">
@@ -7016,13 +7016,13 @@
         <v>0.3906</v>
       </c>
       <c r="K65" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L65" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N65" t="n">
         <v>28332.75</v>
@@ -7043,7 +7043,7 @@
         <v>0.0068</v>
       </c>
       <c r="T65" t="n">
-        <v>8289.85</v>
+        <v>5255.32</v>
       </c>
     </row>
     <row r="66">
@@ -7082,13 +7082,13 @@
         <v>0.3572</v>
       </c>
       <c r="K66" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L66" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N66" t="n">
         <v>11514.05</v>
@@ -7109,7 +7109,7 @@
         <v>0.0262</v>
       </c>
       <c r="T66" t="n">
-        <v>2431.71</v>
+        <v>8623.58</v>
       </c>
     </row>
     <row r="67">
@@ -7151,10 +7151,10 @@
         <v>16</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M67" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N67" t="n">
         <v>24256.51</v>
@@ -7175,7 +7175,7 @@
         <v>0.0227</v>
       </c>
       <c r="T67" t="n">
-        <v>10385.18</v>
+        <v>10227.72</v>
       </c>
     </row>
     <row r="68">
@@ -7214,10 +7214,10 @@
         <v>0.2528</v>
       </c>
       <c r="K68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M68" t="n">
         <v>6</v>
@@ -7241,7 +7241,7 @@
         <v>0.0271</v>
       </c>
       <c r="T68" t="n">
-        <v>5397.67</v>
+        <v>4954.26</v>
       </c>
     </row>
     <row r="69">
@@ -7280,13 +7280,13 @@
         <v>0.2753</v>
       </c>
       <c r="K69" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L69" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M69" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N69" t="n">
         <v>3398.01</v>
@@ -7307,7 +7307,7 @@
         <v>0.0476</v>
       </c>
       <c r="T69" t="n">
-        <v>17786.45</v>
+        <v>35348.54</v>
       </c>
     </row>
     <row r="70">
@@ -7346,13 +7346,13 @@
         <v>0.3381</v>
       </c>
       <c r="K70" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L70" t="n">
         <v>3</v>
       </c>
       <c r="M70" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N70" t="n">
         <v>6132.87</v>
@@ -7373,7 +7373,7 @@
         <v>0.0211</v>
       </c>
       <c r="T70" t="n">
-        <v>16560.14</v>
+        <v>15545.42</v>
       </c>
     </row>
     <row r="71">
@@ -7412,13 +7412,13 @@
         <v>0.3301</v>
       </c>
       <c r="K71" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L71" t="n">
         <v>3</v>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N71" t="n">
         <v>9575.809999999999</v>
@@ -7439,7 +7439,7 @@
         <v>0.0292</v>
       </c>
       <c r="T71" t="n">
-        <v>17336.35</v>
+        <v>1854.69</v>
       </c>
     </row>
     <row r="72">
@@ -7478,13 +7478,13 @@
         <v>0.3108</v>
       </c>
       <c r="K72" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L72" t="n">
+        <v>5</v>
+      </c>
+      <c r="M72" t="n">
         <v>7</v>
-      </c>
-      <c r="M72" t="n">
-        <v>8</v>
       </c>
       <c r="N72" t="n">
         <v>11015.52</v>
@@ -7505,7 +7505,7 @@
         <v>0.0444</v>
       </c>
       <c r="T72" t="n">
-        <v>9064.540000000001</v>
+        <v>6204.43</v>
       </c>
     </row>
     <row r="73">
@@ -7544,13 +7544,13 @@
         <v>0.2951</v>
       </c>
       <c r="K73" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N73" t="n">
         <v>11022.27</v>
@@ -7571,7 +7571,7 @@
         <v>0.045</v>
       </c>
       <c r="T73" t="n">
-        <v>3664.27</v>
+        <v>5902.08</v>
       </c>
     </row>
     <row r="74">
@@ -7610,10 +7610,10 @@
         <v>0.3742</v>
       </c>
       <c r="K74" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L74" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M74" t="n">
         <v>8</v>
@@ -7637,7 +7637,7 @@
         <v>0.0196</v>
       </c>
       <c r="T74" t="n">
-        <v>7708.47</v>
+        <v>5944.63</v>
       </c>
     </row>
     <row r="75">
@@ -7676,13 +7676,13 @@
         <v>0.3821</v>
       </c>
       <c r="K75" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L75" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M75" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N75" t="n">
         <v>17552.07</v>
@@ -7703,7 +7703,7 @@
         <v>0.0493</v>
       </c>
       <c r="T75" t="n">
-        <v>4955.77</v>
+        <v>9128.049999999999</v>
       </c>
     </row>
     <row r="76">
@@ -7742,13 +7742,13 @@
         <v>0.3688</v>
       </c>
       <c r="K76" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N76" t="n">
         <v>13608.04</v>
@@ -7769,7 +7769,7 @@
         <v>0.0352</v>
       </c>
       <c r="T76" t="n">
-        <v>13377.95</v>
+        <v>13740.48</v>
       </c>
     </row>
     <row r="77">
@@ -7808,10 +7808,10 @@
         <v>0.3875</v>
       </c>
       <c r="K77" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M77" t="n">
         <v>6</v>
@@ -7835,7 +7835,7 @@
         <v>0.0251</v>
       </c>
       <c r="T77" t="n">
-        <v>6888.99</v>
+        <v>10125.19</v>
       </c>
     </row>
     <row r="78">
@@ -7874,10 +7874,10 @@
         <v>0.335</v>
       </c>
       <c r="K78" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M78" t="n">
         <v>10</v>
@@ -7901,7 +7901,7 @@
         <v>0.0218</v>
       </c>
       <c r="T78" t="n">
-        <v>11207.02</v>
+        <v>11323.58</v>
       </c>
     </row>
     <row r="79">
@@ -7940,13 +7940,13 @@
         <v>0.2832</v>
       </c>
       <c r="K79" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N79" t="n">
         <v>6508.79</v>
@@ -7967,7 +7967,7 @@
         <v>0.0207</v>
       </c>
       <c r="T79" t="n">
-        <v>12425.86</v>
+        <v>6302.13</v>
       </c>
     </row>
     <row r="80">
@@ -8006,13 +8006,13 @@
         <v>0.3899</v>
       </c>
       <c r="K80" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N80" t="n">
         <v>7662.45</v>
@@ -8033,7 +8033,7 @@
         <v>0.0293</v>
       </c>
       <c r="T80" t="n">
-        <v>5891.11</v>
+        <v>2076.24</v>
       </c>
     </row>
     <row r="81">
@@ -8072,13 +8072,13 @@
         <v>0.3364</v>
       </c>
       <c r="K81" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L81" t="n">
         <v>6</v>
       </c>
       <c r="M81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N81" t="n">
         <v>18499.26</v>
@@ -8099,7 +8099,7 @@
         <v>0.0491</v>
       </c>
       <c r="T81" t="n">
-        <v>6664.12</v>
+        <v>16835.01</v>
       </c>
     </row>
     <row r="82">
@@ -8138,13 +8138,13 @@
         <v>0.365</v>
       </c>
       <c r="K82" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M82" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N82" t="n">
         <v>3843.84</v>
@@ -8165,7 +8165,7 @@
         <v>0.0133</v>
       </c>
       <c r="T82" t="n">
-        <v>9656.209999999999</v>
+        <v>8586.110000000001</v>
       </c>
     </row>
     <row r="83">
@@ -8204,13 +8204,13 @@
         <v>0.4013</v>
       </c>
       <c r="K83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L83" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M83" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N83" t="n">
         <v>30798.29</v>
@@ -8231,7 +8231,7 @@
         <v>0.0408</v>
       </c>
       <c r="T83" t="n">
-        <v>14376.1</v>
+        <v>14641.9</v>
       </c>
     </row>
     <row r="84">
@@ -8270,10 +8270,10 @@
         <v>0.377</v>
       </c>
       <c r="K84" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M84" t="n">
         <v>6</v>
@@ -8297,7 +8297,7 @@
         <v>0.007</v>
       </c>
       <c r="T84" t="n">
-        <v>19839.83</v>
+        <v>9893.16</v>
       </c>
     </row>
     <row r="85">
@@ -8363,7 +8363,7 @@
         <v>0.0211</v>
       </c>
       <c r="T85" t="n">
-        <v>23737.07</v>
+        <v>28132.02</v>
       </c>
     </row>
     <row r="86">
@@ -8402,13 +8402,13 @@
         <v>0.341</v>
       </c>
       <c r="K86" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L86" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M86" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N86" t="n">
         <v>7446.4</v>
@@ -8429,7 +8429,7 @@
         <v>0.0183</v>
       </c>
       <c r="T86" t="n">
-        <v>17890.87</v>
+        <v>13563.39</v>
       </c>
     </row>
     <row r="87">
@@ -8468,13 +8468,13 @@
         <v>0.4476</v>
       </c>
       <c r="K87" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="L87" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M87" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="N87" t="n">
         <v>10803.87</v>
@@ -8495,7 +8495,7 @@
         <v>0.0372</v>
       </c>
       <c r="T87" t="n">
-        <v>8399.48</v>
+        <v>15696.64</v>
       </c>
     </row>
     <row r="88">
@@ -8561,7 +8561,7 @@
         <v>0.032</v>
       </c>
       <c r="T88" t="n">
-        <v>6244.7</v>
+        <v>6295.54</v>
       </c>
     </row>
     <row r="89">
@@ -8603,10 +8603,10 @@
         <v>14</v>
       </c>
       <c r="L89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N89" t="n">
         <v>11530.46</v>
@@ -8627,7 +8627,7 @@
         <v>0.0077</v>
       </c>
       <c r="T89" t="n">
-        <v>6616.23</v>
+        <v>14033.05</v>
       </c>
     </row>
     <row r="90">
@@ -8666,13 +8666,13 @@
         <v>0.2817</v>
       </c>
       <c r="K90" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M90" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N90" t="n">
         <v>10599.21</v>
@@ -8693,7 +8693,7 @@
         <v>0.0113</v>
       </c>
       <c r="T90" t="n">
-        <v>25948.18</v>
+        <v>15387.9</v>
       </c>
     </row>
     <row r="91">
@@ -8732,13 +8732,13 @@
         <v>0.3423</v>
       </c>
       <c r="K91" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L91" t="n">
         <v>9</v>
       </c>
       <c r="M91" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N91" t="n">
         <v>17827.07</v>
@@ -8759,7 +8759,7 @@
         <v>0.0453</v>
       </c>
       <c r="T91" t="n">
-        <v>25864.28</v>
+        <v>25987.22</v>
       </c>
     </row>
     <row r="92">
@@ -8798,13 +8798,13 @@
         <v>0.4169</v>
       </c>
       <c r="K92" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L92" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M92" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N92" t="n">
         <v>7139.81</v>
@@ -8825,7 +8825,7 @@
         <v>0.017</v>
       </c>
       <c r="T92" t="n">
-        <v>8255.709999999999</v>
+        <v>8764.49</v>
       </c>
     </row>
     <row r="93">
@@ -8864,13 +8864,13 @@
         <v>0.3516</v>
       </c>
       <c r="K93" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M93" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N93" t="n">
         <v>3846.4</v>
@@ -8891,7 +8891,7 @@
         <v>0.0281</v>
       </c>
       <c r="T93" t="n">
-        <v>15113.54</v>
+        <v>22275.06</v>
       </c>
     </row>
     <row r="94">
@@ -8930,10 +8930,10 @@
         <v>0.4368</v>
       </c>
       <c r="K94" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L94" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M94" t="n">
         <v>8</v>
@@ -8957,7 +8957,7 @@
         <v>0.0183</v>
       </c>
       <c r="T94" t="n">
-        <v>27071.93</v>
+        <v>12522.69</v>
       </c>
     </row>
     <row r="95">
@@ -8996,10 +8996,10 @@
         <v>0.4498</v>
       </c>
       <c r="K95" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L95" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M95" t="n">
         <v>5</v>
@@ -9023,7 +9023,7 @@
         <v>0.044</v>
       </c>
       <c r="T95" t="n">
-        <v>5814.97</v>
+        <v>13834.69</v>
       </c>
     </row>
     <row r="96">
@@ -9062,13 +9062,13 @@
         <v>0.3587</v>
       </c>
       <c r="K96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N96" t="n">
         <v>5998.14</v>
@@ -9089,7 +9089,7 @@
         <v>0.0436</v>
       </c>
       <c r="T96" t="n">
-        <v>3060.6</v>
+        <v>2442.23</v>
       </c>
     </row>
     <row r="97">
@@ -9128,10 +9128,10 @@
         <v>0.2967</v>
       </c>
       <c r="K97" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L97" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M97" t="n">
         <v>4</v>
@@ -9155,7 +9155,7 @@
         <v>0.0265</v>
       </c>
       <c r="T97" t="n">
-        <v>5331.24</v>
+        <v>4808.83</v>
       </c>
     </row>
     <row r="98">
@@ -9194,13 +9194,13 @@
         <v>0.3827</v>
       </c>
       <c r="K98" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L98" t="n">
         <v>6</v>
       </c>
       <c r="M98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N98" t="n">
         <v>2758.16</v>
@@ -9221,7 +9221,7 @@
         <v>0.0136</v>
       </c>
       <c r="T98" t="n">
-        <v>7549.14</v>
+        <v>6521.98</v>
       </c>
     </row>
     <row r="99">
@@ -9260,13 +9260,13 @@
         <v>0.368</v>
       </c>
       <c r="K99" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L99" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M99" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N99" t="n">
         <v>8103.31</v>
@@ -9287,7 +9287,7 @@
         <v>0.0138</v>
       </c>
       <c r="T99" t="n">
-        <v>2268.18</v>
+        <v>8583.76</v>
       </c>
     </row>
     <row r="100">
@@ -9326,13 +9326,13 @@
         <v>0.3945</v>
       </c>
       <c r="K100" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L100" t="n">
         <v>8</v>
       </c>
       <c r="M100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N100" t="n">
         <v>4273.71</v>
@@ -9353,7 +9353,7 @@
         <v>0.0117</v>
       </c>
       <c r="T100" t="n">
-        <v>8297.030000000001</v>
+        <v>9256.68</v>
       </c>
     </row>
     <row r="101">
@@ -9392,13 +9392,13 @@
         <v>0.3177</v>
       </c>
       <c r="K101" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L101" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M101" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N101" t="n">
         <v>7311.58</v>
@@ -9419,7 +9419,7 @@
         <v>0.0167</v>
       </c>
       <c r="T101" t="n">
-        <v>24187.45</v>
+        <v>19679.69</v>
       </c>
     </row>
     <row r="102">
@@ -9458,13 +9458,13 @@
         <v>0.326</v>
       </c>
       <c r="K102" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L102" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M102" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N102" t="n">
         <v>8265.41</v>
@@ -9485,7 +9485,7 @@
         <v>0.0438</v>
       </c>
       <c r="T102" t="n">
-        <v>13786.5</v>
+        <v>14383.85</v>
       </c>
     </row>
     <row r="103">
@@ -9524,10 +9524,10 @@
         <v>0.2637</v>
       </c>
       <c r="K103" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L103" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M103" t="n">
         <v>5</v>
@@ -9551,7 +9551,7 @@
         <v>0.0379</v>
       </c>
       <c r="T103" t="n">
-        <v>10781.98</v>
+        <v>8444.32</v>
       </c>
     </row>
     <row r="104">
@@ -9590,13 +9590,13 @@
         <v>0.3767</v>
       </c>
       <c r="K104" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N104" t="n">
         <v>35727.02</v>
@@ -9617,7 +9617,7 @@
         <v>0.0263</v>
       </c>
       <c r="T104" t="n">
-        <v>2163.53</v>
+        <v>4034.19</v>
       </c>
     </row>
     <row r="105">
@@ -9656,13 +9656,13 @@
         <v>0.4092</v>
       </c>
       <c r="K105" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L105" t="n">
         <v>8</v>
       </c>
       <c r="M105" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N105" t="n">
         <v>12048.69</v>
@@ -9683,7 +9683,7 @@
         <v>0.0296</v>
       </c>
       <c r="T105" t="n">
-        <v>16312.38</v>
+        <v>19373.39</v>
       </c>
     </row>
     <row r="106">
@@ -9722,13 +9722,13 @@
         <v>0.4085</v>
       </c>
       <c r="K106" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L106" t="n">
+        <v>7</v>
+      </c>
+      <c r="M106" t="n">
         <v>6</v>
-      </c>
-      <c r="M106" t="n">
-        <v>8</v>
       </c>
       <c r="N106" t="n">
         <v>24113.31</v>
@@ -9749,7 +9749,7 @@
         <v>0.0335</v>
       </c>
       <c r="T106" t="n">
-        <v>10816.11</v>
+        <v>9785.639999999999</v>
       </c>
     </row>
     <row r="107">
@@ -9788,10 +9788,10 @@
         <v>0.4326</v>
       </c>
       <c r="K107" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L107" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M107" t="n">
         <v>5</v>
@@ -9815,7 +9815,7 @@
         <v>0.0252</v>
       </c>
       <c r="T107" t="n">
-        <v>17551.05</v>
+        <v>15895.43</v>
       </c>
     </row>
     <row r="108">
@@ -9854,10 +9854,10 @@
         <v>0.4109</v>
       </c>
       <c r="K108" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L108" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M108" t="n">
         <v>8</v>
@@ -9881,7 +9881,7 @@
         <v>0.0205</v>
       </c>
       <c r="T108" t="n">
-        <v>17263.49</v>
+        <v>16890.72</v>
       </c>
     </row>
     <row r="109">
@@ -9920,13 +9920,13 @@
         <v>0.3675</v>
       </c>
       <c r="K109" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L109" t="n">
+        <v>4</v>
+      </c>
+      <c r="M109" t="n">
         <v>6</v>
-      </c>
-      <c r="M109" t="n">
-        <v>8</v>
       </c>
       <c r="N109" t="n">
         <v>26621.36</v>
@@ -9947,7 +9947,7 @@
         <v>0.0142</v>
       </c>
       <c r="T109" t="n">
-        <v>12023.14</v>
+        <v>10150.33</v>
       </c>
     </row>
     <row r="110">
@@ -9986,13 +9986,13 @@
         <v>0.3466</v>
       </c>
       <c r="K110" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L110" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M110" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N110" t="n">
         <v>11092.15</v>
@@ -10013,7 +10013,7 @@
         <v>0.0461</v>
       </c>
       <c r="T110" t="n">
-        <v>7707.86</v>
+        <v>6669.16</v>
       </c>
     </row>
     <row r="111">
@@ -10052,13 +10052,13 @@
         <v>0.4456</v>
       </c>
       <c r="K111" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L111" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M111" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N111" t="n">
         <v>15723.86</v>
@@ -10079,7 +10079,7 @@
         <v>0.0373</v>
       </c>
       <c r="T111" t="n">
-        <v>12227.43</v>
+        <v>13815.86</v>
       </c>
     </row>
     <row r="112">
@@ -10118,13 +10118,13 @@
         <v>0.2598</v>
       </c>
       <c r="K112" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L112" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M112" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N112" t="n">
         <v>15482.33</v>
@@ -10145,7 +10145,7 @@
         <v>0.0241</v>
       </c>
       <c r="T112" t="n">
-        <v>5834.01</v>
+        <v>8204.110000000001</v>
       </c>
     </row>
     <row r="113">
@@ -10184,13 +10184,13 @@
         <v>0.3714</v>
       </c>
       <c r="K113" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L113" t="n">
+        <v>4</v>
+      </c>
+      <c r="M113" t="n">
         <v>5</v>
-      </c>
-      <c r="M113" t="n">
-        <v>6</v>
       </c>
       <c r="N113" t="n">
         <v>26159.92</v>
@@ -10211,7 +10211,7 @@
         <v>0.0343</v>
       </c>
       <c r="T113" t="n">
-        <v>5268.55</v>
+        <v>3348.79</v>
       </c>
     </row>
     <row r="114">
@@ -10250,13 +10250,13 @@
         <v>0.3818</v>
       </c>
       <c r="K114" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L114" t="n">
         <v>10</v>
       </c>
       <c r="M114" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N114" t="n">
         <v>7146.32</v>
@@ -10277,7 +10277,7 @@
         <v>0.0361</v>
       </c>
       <c r="T114" t="n">
-        <v>10333.43</v>
+        <v>11054.81</v>
       </c>
     </row>
     <row r="115">
@@ -10316,10 +10316,10 @@
         <v>0.3382</v>
       </c>
       <c r="K115" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L115" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M115" t="n">
         <v>4</v>
@@ -10343,7 +10343,7 @@
         <v>0.0177</v>
       </c>
       <c r="T115" t="n">
-        <v>7028.1</v>
+        <v>5306.65</v>
       </c>
     </row>
     <row r="116">
@@ -10382,10 +10382,10 @@
         <v>0.2764</v>
       </c>
       <c r="K116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M116" t="n">
         <v>9</v>
@@ -10409,7 +10409,7 @@
         <v>0.0411</v>
       </c>
       <c r="T116" t="n">
-        <v>16677.22</v>
+        <v>17420.06</v>
       </c>
     </row>
     <row r="117">
@@ -10448,13 +10448,13 @@
         <v>0.3014</v>
       </c>
       <c r="K117" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L117" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M117" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N117" t="n">
         <v>31240.99</v>
@@ -10475,7 +10475,7 @@
         <v>0.0483</v>
       </c>
       <c r="T117" t="n">
-        <v>7918.78</v>
+        <v>17351.43</v>
       </c>
     </row>
     <row r="118">
@@ -10541,7 +10541,7 @@
         <v>0.0068</v>
       </c>
       <c r="T118" t="n">
-        <v>9055.940000000001</v>
+        <v>10008.31</v>
       </c>
     </row>
     <row r="119">
@@ -10583,10 +10583,10 @@
         <v>11</v>
       </c>
       <c r="L119" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N119" t="n">
         <v>16840.71</v>
@@ -10607,7 +10607,7 @@
         <v>0.0297</v>
       </c>
       <c r="T119" t="n">
-        <v>8372.25</v>
+        <v>7529.57</v>
       </c>
     </row>
     <row r="120">
@@ -10646,13 +10646,13 @@
         <v>0.3573</v>
       </c>
       <c r="K120" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L120" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M120" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N120" t="n">
         <v>13411.63</v>
@@ -10673,7 +10673,7 @@
         <v>0.0329</v>
       </c>
       <c r="T120" t="n">
-        <v>11233.48</v>
+        <v>4223.66</v>
       </c>
     </row>
     <row r="121">
@@ -10712,13 +10712,13 @@
         <v>0.4381</v>
       </c>
       <c r="K121" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L121" t="n">
         <v>6</v>
       </c>
       <c r="M121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
         <v>11718.79</v>
@@ -10739,7 +10739,7 @@
         <v>0.0424</v>
       </c>
       <c r="T121" t="n">
-        <v>7568.95</v>
+        <v>4293.59</v>
       </c>
     </row>
     <row r="122">
@@ -10778,13 +10778,13 @@
         <v>0.2943</v>
       </c>
       <c r="K122" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M122" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N122" t="n">
         <v>8978.16</v>
@@ -10805,7 +10805,7 @@
         <v>0.0494</v>
       </c>
       <c r="T122" t="n">
-        <v>7775.84</v>
+        <v>5969.27</v>
       </c>
     </row>
     <row r="123">
@@ -10844,13 +10844,13 @@
         <v>0.278</v>
       </c>
       <c r="K123" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L123" t="n">
         <v>7</v>
       </c>
       <c r="M123" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N123" t="n">
         <v>11107.76</v>
@@ -10871,7 +10871,7 @@
         <v>0.0114</v>
       </c>
       <c r="T123" t="n">
-        <v>18966.8</v>
+        <v>19649.84</v>
       </c>
     </row>
     <row r="124">
@@ -10910,13 +10910,13 @@
         <v>0.2771</v>
       </c>
       <c r="K124" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L124" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M124" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N124" t="n">
         <v>10484.19</v>
@@ -10937,7 +10937,7 @@
         <v>0.029</v>
       </c>
       <c r="T124" t="n">
-        <v>10990.36</v>
+        <v>11745.81</v>
       </c>
     </row>
     <row r="125">
@@ -11003,7 +11003,7 @@
         <v>0.0464</v>
       </c>
       <c r="T125" t="n">
-        <v>7646.38</v>
+        <v>8181.91</v>
       </c>
     </row>
     <row r="126">
@@ -11069,7 +11069,7 @@
         <v>0.0294</v>
       </c>
       <c r="T126" t="n">
-        <v>7358.49</v>
+        <v>7627.27</v>
       </c>
     </row>
     <row r="127">
@@ -11108,13 +11108,13 @@
         <v>0.2699</v>
       </c>
       <c r="K127" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L127" t="n">
+        <v>4</v>
+      </c>
+      <c r="M127" t="n">
         <v>6</v>
-      </c>
-      <c r="M127" t="n">
-        <v>7</v>
       </c>
       <c r="N127" t="n">
         <v>12087.1</v>
@@ -11135,7 +11135,7 @@
         <v>0.0419</v>
       </c>
       <c r="T127" t="n">
-        <v>6220.57</v>
+        <v>5784.34</v>
       </c>
     </row>
     <row r="128">
@@ -11174,13 +11174,13 @@
         <v>0.2744</v>
       </c>
       <c r="K128" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L128" t="n">
         <v>5</v>
       </c>
       <c r="M128" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N128" t="n">
         <v>18845.35</v>
@@ -11201,7 +11201,7 @@
         <v>0.0227</v>
       </c>
       <c r="T128" t="n">
-        <v>6292.2</v>
+        <v>5493.07</v>
       </c>
     </row>
     <row r="129">
@@ -11240,13 +11240,13 @@
         <v>0.2543</v>
       </c>
       <c r="K129" t="n">
+        <v>15</v>
+      </c>
+      <c r="L129" t="n">
         <v>9</v>
       </c>
-      <c r="L129" t="n">
+      <c r="M129" t="n">
         <v>6</v>
-      </c>
-      <c r="M129" t="n">
-        <v>3</v>
       </c>
       <c r="N129" t="n">
         <v>20561.73</v>
@@ -11267,7 +11267,7 @@
         <v>0.0066</v>
       </c>
       <c r="T129" t="n">
-        <v>5106.07</v>
+        <v>6677.96</v>
       </c>
     </row>
     <row r="130">
@@ -11333,7 +11333,7 @@
         <v>0.0451</v>
       </c>
       <c r="T130" t="n">
-        <v>6481.04</v>
+        <v>6161.45</v>
       </c>
     </row>
     <row r="131">
@@ -11375,10 +11375,10 @@
         <v>13</v>
       </c>
       <c r="L131" t="n">
+        <v>6</v>
+      </c>
+      <c r="M131" t="n">
         <v>7</v>
-      </c>
-      <c r="M131" t="n">
-        <v>6</v>
       </c>
       <c r="N131" t="n">
         <v>4916.77</v>
@@ -11399,7 +11399,7 @@
         <v>0.0072</v>
       </c>
       <c r="T131" t="n">
-        <v>2515.21</v>
+        <v>3007.53</v>
       </c>
     </row>
     <row r="132">
@@ -11438,10 +11438,10 @@
         <v>0.2849</v>
       </c>
       <c r="K132" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L132" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M132" t="n">
         <v>8</v>
@@ -11465,7 +11465,7 @@
         <v>0.0287</v>
       </c>
       <c r="T132" t="n">
-        <v>4561.24</v>
+        <v>4292.93</v>
       </c>
     </row>
     <row r="133">
@@ -11504,13 +11504,13 @@
         <v>0.3148</v>
       </c>
       <c r="K133" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L133" t="n">
         <v>2</v>
       </c>
       <c r="M133" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N133" t="n">
         <v>10368.39</v>
@@ -11531,7 +11531,7 @@
         <v>0.0325</v>
       </c>
       <c r="T133" t="n">
-        <v>6115.04</v>
+        <v>5437.86</v>
       </c>
     </row>
     <row r="134">
@@ -11570,10 +11570,10 @@
         <v>0.4056</v>
       </c>
       <c r="K134" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L134" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M134" t="n">
         <v>11</v>
@@ -11597,7 +11597,7 @@
         <v>0.0253</v>
       </c>
       <c r="T134" t="n">
-        <v>8471.15</v>
+        <v>9036.129999999999</v>
       </c>
     </row>
     <row r="135">
@@ -11636,13 +11636,13 @@
         <v>0.4066</v>
       </c>
       <c r="K135" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L135" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M135" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N135" t="n">
         <v>4994.44</v>
@@ -11663,7 +11663,7 @@
         <v>0.0402</v>
       </c>
       <c r="T135" t="n">
-        <v>4346.69</v>
+        <v>7463.24</v>
       </c>
     </row>
     <row r="136">
@@ -11702,13 +11702,13 @@
         <v>0.3458</v>
       </c>
       <c r="K136" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L136" t="n">
         <v>5</v>
       </c>
       <c r="M136" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N136" t="n">
         <v>1408.47</v>
@@ -11729,7 +11729,7 @@
         <v>0.0295</v>
       </c>
       <c r="T136" t="n">
-        <v>4857.21</v>
+        <v>7507.54</v>
       </c>
     </row>
     <row r="137">
@@ -11768,13 +11768,13 @@
         <v>0.2662</v>
       </c>
       <c r="K137" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M137" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N137" t="n">
         <v>2078.12</v>
@@ -11795,7 +11795,7 @@
         <v>0.0165</v>
       </c>
       <c r="T137" t="n">
-        <v>11153.16</v>
+        <v>8449.690000000001</v>
       </c>
     </row>
     <row r="138">
@@ -11834,13 +11834,13 @@
         <v>0.315</v>
       </c>
       <c r="K138" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L138" t="n">
+        <v>6</v>
+      </c>
+      <c r="M138" t="n">
         <v>5</v>
-      </c>
-      <c r="M138" t="n">
-        <v>7</v>
       </c>
       <c r="N138" t="n">
         <v>2192.36</v>
@@ -11861,7 +11861,7 @@
         <v>0.0055</v>
       </c>
       <c r="T138" t="n">
-        <v>6423.93</v>
+        <v>5201.97</v>
       </c>
     </row>
     <row r="139">
@@ -11900,10 +11900,10 @@
         <v>0.3904</v>
       </c>
       <c r="K139" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L139" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M139" t="n">
         <v>3</v>
@@ -11927,7 +11927,7 @@
         <v>0.019</v>
       </c>
       <c r="T139" t="n">
-        <v>8117.03</v>
+        <v>5710.6</v>
       </c>
     </row>
     <row r="140">
@@ -11966,10 +11966,10 @@
         <v>0.2957</v>
       </c>
       <c r="K140" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M140" t="n">
         <v>9</v>
@@ -11993,7 +11993,7 @@
         <v>0.0328</v>
       </c>
       <c r="T140" t="n">
-        <v>22014.52</v>
+        <v>20259.33</v>
       </c>
     </row>
     <row r="141">
@@ -12032,10 +12032,10 @@
         <v>0.383</v>
       </c>
       <c r="K141" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L141" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M141" t="n">
         <v>9</v>
@@ -12059,7 +12059,7 @@
         <v>0.0271</v>
       </c>
       <c r="T141" t="n">
-        <v>7843.43</v>
+        <v>7339.09</v>
       </c>
     </row>
     <row r="142">
@@ -12098,10 +12098,10 @@
         <v>0.2686</v>
       </c>
       <c r="K142" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L142" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M142" t="n">
         <v>4</v>
@@ -12125,7 +12125,7 @@
         <v>0.0281</v>
       </c>
       <c r="T142" t="n">
-        <v>7997.88</v>
+        <v>3491.43</v>
       </c>
     </row>
     <row r="143">
@@ -12164,13 +12164,13 @@
         <v>0.3623</v>
       </c>
       <c r="K143" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L143" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M143" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N143" t="n">
         <v>11024.13</v>
@@ -12191,7 +12191,7 @@
         <v>0.0447</v>
       </c>
       <c r="T143" t="n">
-        <v>19979.91</v>
+        <v>24398.86</v>
       </c>
     </row>
     <row r="144">
@@ -12233,10 +12233,10 @@
         <v>12</v>
       </c>
       <c r="L144" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M144" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N144" t="n">
         <v>4327.74</v>
@@ -12257,7 +12257,7 @@
         <v>0.0214</v>
       </c>
       <c r="T144" t="n">
-        <v>12287.13</v>
+        <v>12204.16</v>
       </c>
     </row>
     <row r="145">
@@ -12296,13 +12296,13 @@
         <v>0.2925</v>
       </c>
       <c r="K145" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L145" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M145" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N145" t="n">
         <v>12660.13</v>
@@ -12323,7 +12323,7 @@
         <v>0.0066</v>
       </c>
       <c r="T145" t="n">
-        <v>26663.73</v>
+        <v>29093.73</v>
       </c>
     </row>
     <row r="146">
@@ -12389,7 +12389,7 @@
         <v>0.0421</v>
       </c>
       <c r="T146" t="n">
-        <v>17811.9</v>
+        <v>16678.08</v>
       </c>
     </row>
     <row r="147">
@@ -12428,13 +12428,13 @@
         <v>0.3785</v>
       </c>
       <c r="K147" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L147" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M147" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N147" t="n">
         <v>12571.57</v>
@@ -12455,7 +12455,7 @@
         <v>0.0407</v>
       </c>
       <c r="T147" t="n">
-        <v>5013.41</v>
+        <v>11795.6</v>
       </c>
     </row>
     <row r="148">
@@ -12494,13 +12494,13 @@
         <v>0.3905</v>
       </c>
       <c r="K148" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L148" t="n">
+        <v>16</v>
+      </c>
+      <c r="M148" t="n">
         <v>11</v>
-      </c>
-      <c r="M148" t="n">
-        <v>10</v>
       </c>
       <c r="N148" t="n">
         <v>2488.05</v>
@@ -12521,7 +12521,7 @@
         <v>0.0475</v>
       </c>
       <c r="T148" t="n">
-        <v>15474.75</v>
+        <v>16259.02</v>
       </c>
     </row>
     <row r="149">
@@ -12560,13 +12560,13 @@
         <v>0.3302</v>
       </c>
       <c r="K149" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L149" t="n">
         <v>7</v>
       </c>
       <c r="M149" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N149" t="n">
         <v>4285.47</v>
@@ -12587,7 +12587,7 @@
         <v>0.0416</v>
       </c>
       <c r="T149" t="n">
-        <v>15778.29</v>
+        <v>15724.09</v>
       </c>
     </row>
     <row r="150">
@@ -12626,13 +12626,13 @@
         <v>0.334</v>
       </c>
       <c r="K150" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L150" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M150" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N150" t="n">
         <v>11716.67</v>
@@ -12653,7 +12653,7 @@
         <v>0.0167</v>
       </c>
       <c r="T150" t="n">
-        <v>12467.42</v>
+        <v>7103.08</v>
       </c>
     </row>
     <row r="151">
@@ -12692,13 +12692,13 @@
         <v>0.267</v>
       </c>
       <c r="K151" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L151" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M151" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N151" t="n">
         <v>8291.879999999999</v>
@@ -12719,7 +12719,7 @@
         <v>0.0308</v>
       </c>
       <c r="T151" t="n">
-        <v>5316.42</v>
+        <v>4302.32</v>
       </c>
     </row>
     <row r="152">
@@ -12758,13 +12758,13 @@
         <v>0.3471</v>
       </c>
       <c r="K152" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L152" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M152" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N152" t="n">
         <v>13822.75</v>
@@ -12785,7 +12785,7 @@
         <v>0.0474</v>
       </c>
       <c r="T152" t="n">
-        <v>6205.43</v>
+        <v>4203.02</v>
       </c>
     </row>
     <row r="153">
@@ -12824,13 +12824,13 @@
         <v>0.3066</v>
       </c>
       <c r="K153" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M153" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N153" t="n">
         <v>14447.83</v>
@@ -12851,7 +12851,7 @@
         <v>0.012</v>
       </c>
       <c r="T153" t="n">
-        <v>5753.73</v>
+        <v>12336.94</v>
       </c>
     </row>
     <row r="154">
@@ -12890,13 +12890,13 @@
         <v>0.3699</v>
       </c>
       <c r="K154" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M154" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N154" t="n">
         <v>14059.74</v>
@@ -12917,7 +12917,7 @@
         <v>0.0411</v>
       </c>
       <c r="T154" t="n">
-        <v>9367.040000000001</v>
+        <v>9933.299999999999</v>
       </c>
     </row>
     <row r="155">
@@ -12959,10 +12959,10 @@
         <v>10</v>
       </c>
       <c r="L155" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M155" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N155" t="n">
         <v>4452.22</v>
@@ -12983,7 +12983,7 @@
         <v>0.0316</v>
       </c>
       <c r="T155" t="n">
-        <v>5170.61</v>
+        <v>4168.85</v>
       </c>
     </row>
     <row r="156">
@@ -13049,7 +13049,7 @@
         <v>0.031</v>
       </c>
       <c r="T156" t="n">
-        <v>26161.11</v>
+        <v>22715.71</v>
       </c>
     </row>
     <row r="157">
@@ -13088,13 +13088,13 @@
         <v>0.2537</v>
       </c>
       <c r="K157" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L157" t="n">
         <v>2</v>
       </c>
       <c r="M157" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N157" t="n">
         <v>2881.39</v>
@@ -13115,7 +13115,7 @@
         <v>0.008</v>
       </c>
       <c r="T157" t="n">
-        <v>7569.05</v>
+        <v>6869.15</v>
       </c>
     </row>
     <row r="158">
@@ -13154,13 +13154,13 @@
         <v>0.273</v>
       </c>
       <c r="K158" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L158" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M158" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N158" t="n">
         <v>5530.58</v>
@@ -13181,7 +13181,7 @@
         <v>0.0469</v>
       </c>
       <c r="T158" t="n">
-        <v>13746.33</v>
+        <v>13567.8</v>
       </c>
     </row>
     <row r="159">
@@ -13220,13 +13220,13 @@
         <v>0.434</v>
       </c>
       <c r="K159" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L159" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M159" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N159" t="n">
         <v>37771.52</v>
@@ -13247,7 +13247,7 @@
         <v>0.0054</v>
       </c>
       <c r="T159" t="n">
-        <v>4847.16</v>
+        <v>5498.63</v>
       </c>
     </row>
     <row r="160">
@@ -13286,13 +13286,13 @@
         <v>0.3292</v>
       </c>
       <c r="K160" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L160" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M160" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N160" t="n">
         <v>34534.2</v>
@@ -13313,7 +13313,7 @@
         <v>0.035</v>
       </c>
       <c r="T160" t="n">
-        <v>9228.139999999999</v>
+        <v>14203.23</v>
       </c>
     </row>
     <row r="161">
@@ -13352,10 +13352,10 @@
         <v>0.2728</v>
       </c>
       <c r="K161" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L161" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M161" t="n">
         <v>4</v>
@@ -13379,7 +13379,7 @@
         <v>0.0436</v>
       </c>
       <c r="T161" t="n">
-        <v>12592.19</v>
+        <v>12536.81</v>
       </c>
     </row>
     <row r="162">
@@ -13418,13 +13418,13 @@
         <v>0.413</v>
       </c>
       <c r="K162" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L162" t="n">
         <v>4</v>
       </c>
       <c r="M162" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N162" t="n">
         <v>42967.9</v>
@@ -13445,7 +13445,7 @@
         <v>0.0147</v>
       </c>
       <c r="T162" t="n">
-        <v>11651.88</v>
+        <v>5728.41</v>
       </c>
     </row>
     <row r="163">
@@ -13484,10 +13484,10 @@
         <v>0.3811</v>
       </c>
       <c r="K163" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L163" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M163" t="n">
         <v>6</v>
@@ -13511,7 +13511,7 @@
         <v>0.0209</v>
       </c>
       <c r="T163" t="n">
-        <v>7340.51</v>
+        <v>7871.33</v>
       </c>
     </row>
     <row r="164">
@@ -13550,10 +13550,10 @@
         <v>0.4348</v>
       </c>
       <c r="K164" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L164" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M164" t="n">
         <v>10</v>
@@ -13577,7 +13577,7 @@
         <v>0.0122</v>
       </c>
       <c r="T164" t="n">
-        <v>16835.73</v>
+        <v>11442.66</v>
       </c>
     </row>
     <row r="165">
@@ -13616,13 +13616,13 @@
         <v>0.2802</v>
       </c>
       <c r="K165" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M165" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N165" t="n">
         <v>11122.02</v>
@@ -13643,7 +13643,7 @@
         <v>0.0119</v>
       </c>
       <c r="T165" t="n">
-        <v>7997.37</v>
+        <v>19152.49</v>
       </c>
     </row>
     <row r="166">
@@ -13682,10 +13682,10 @@
         <v>0.3515</v>
       </c>
       <c r="K166" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L166" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M166" t="n">
         <v>4</v>
@@ -13709,7 +13709,7 @@
         <v>0.0203</v>
       </c>
       <c r="T166" t="n">
-        <v>5568.01</v>
+        <v>6945.46</v>
       </c>
     </row>
     <row r="167">
@@ -13748,13 +13748,13 @@
         <v>0.4229</v>
       </c>
       <c r="K167" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L167" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M167" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N167" t="n">
         <v>17101.2</v>
@@ -13775,7 +13775,7 @@
         <v>0.0179</v>
       </c>
       <c r="T167" t="n">
-        <v>19021.3</v>
+        <v>12827.36</v>
       </c>
     </row>
     <row r="168">
@@ -13814,13 +13814,13 @@
         <v>0.4084</v>
       </c>
       <c r="K168" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L168" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M168" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N168" t="n">
         <v>5040.59</v>
@@ -13841,7 +13841,7 @@
         <v>0.0055</v>
       </c>
       <c r="T168" t="n">
-        <v>13894.55</v>
+        <v>8809.889999999999</v>
       </c>
     </row>
     <row r="169">
@@ -13880,13 +13880,13 @@
         <v>0.3451</v>
       </c>
       <c r="K169" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L169" t="n">
         <v>5</v>
       </c>
       <c r="M169" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N169" t="n">
         <v>20435.91</v>
@@ -13907,7 +13907,7 @@
         <v>0.0424</v>
       </c>
       <c r="T169" t="n">
-        <v>8091.22</v>
+        <v>12230.32</v>
       </c>
     </row>
     <row r="170">
@@ -13973,7 +13973,7 @@
         <v>0.0375</v>
       </c>
       <c r="T170" t="n">
-        <v>6986.5</v>
+        <v>8420.02</v>
       </c>
     </row>
     <row r="171">
@@ -14012,13 +14012,13 @@
         <v>0.2817</v>
       </c>
       <c r="K171" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L171" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M171" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N171" t="n">
         <v>7650.67</v>
@@ -14039,7 +14039,7 @@
         <v>0.0111</v>
       </c>
       <c r="T171" t="n">
-        <v>17050.21</v>
+        <v>10506.57</v>
       </c>
     </row>
     <row r="172">
@@ -14078,13 +14078,13 @@
         <v>0.4078</v>
       </c>
       <c r="K172" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L172" t="n">
         <v>7</v>
       </c>
       <c r="M172" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N172" t="n">
         <v>1966.71</v>
@@ -14105,7 +14105,7 @@
         <v>0.0452</v>
       </c>
       <c r="T172" t="n">
-        <v>8398.59</v>
+        <v>9392.129999999999</v>
       </c>
     </row>
     <row r="173">
@@ -14144,13 +14144,13 @@
         <v>0.3947</v>
       </c>
       <c r="K173" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L173" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M173" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N173" t="n">
         <v>6283.93</v>
@@ -14171,7 +14171,7 @@
         <v>0.0367</v>
       </c>
       <c r="T173" t="n">
-        <v>10796.79</v>
+        <v>15193.33</v>
       </c>
     </row>
     <row r="174">
@@ -14213,10 +14213,10 @@
         <v>10</v>
       </c>
       <c r="L174" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M174" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N174" t="n">
         <v>6095.82</v>
@@ -14237,7 +14237,7 @@
         <v>0.0197</v>
       </c>
       <c r="T174" t="n">
-        <v>3779.83</v>
+        <v>3325.97</v>
       </c>
     </row>
     <row r="175">
@@ -14276,13 +14276,13 @@
         <v>0.4376</v>
       </c>
       <c r="K175" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L175" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N175" t="n">
         <v>11365.09</v>
@@ -14303,7 +14303,7 @@
         <v>0.0288</v>
       </c>
       <c r="T175" t="n">
-        <v>5362.91</v>
+        <v>5536.81</v>
       </c>
     </row>
     <row r="176">
@@ -14345,10 +14345,10 @@
         <v>17</v>
       </c>
       <c r="L176" t="n">
+        <v>9</v>
+      </c>
+      <c r="M176" t="n">
         <v>8</v>
-      </c>
-      <c r="M176" t="n">
-        <v>9</v>
       </c>
       <c r="N176" t="n">
         <v>30200.13</v>
@@ -14369,7 +14369,7 @@
         <v>0.0173</v>
       </c>
       <c r="T176" t="n">
-        <v>16296.84</v>
+        <v>9235.68</v>
       </c>
     </row>
     <row r="177">
@@ -14408,13 +14408,13 @@
         <v>0.3225</v>
       </c>
       <c r="K177" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L177" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M177" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N177" t="n">
         <v>21610.25</v>
@@ -14435,7 +14435,7 @@
         <v>0.0261</v>
       </c>
       <c r="T177" t="n">
-        <v>4360.92</v>
+        <v>11501.14</v>
       </c>
     </row>
     <row r="178">
@@ -14474,10 +14474,10 @@
         <v>0.2775</v>
       </c>
       <c r="K178" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L178" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M178" t="n">
         <v>8</v>
@@ -14501,7 +14501,7 @@
         <v>0.0228</v>
       </c>
       <c r="T178" t="n">
-        <v>14802.15</v>
+        <v>18256.98</v>
       </c>
     </row>
     <row r="179">
@@ -14540,13 +14540,13 @@
         <v>0.4267</v>
       </c>
       <c r="K179" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L179" t="n">
+        <v>3</v>
+      </c>
+      <c r="M179" t="n">
         <v>4</v>
-      </c>
-      <c r="M179" t="n">
-        <v>8</v>
       </c>
       <c r="N179" t="n">
         <v>13171.86</v>
@@ -14567,7 +14567,7 @@
         <v>0.0406</v>
       </c>
       <c r="T179" t="n">
-        <v>12273.03</v>
+        <v>8792.23</v>
       </c>
     </row>
     <row r="180">
@@ -14606,13 +14606,13 @@
         <v>0.2824</v>
       </c>
       <c r="K180" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L180" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M180" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N180" t="n">
         <v>18038.54</v>
@@ -14633,7 +14633,7 @@
         <v>0.0374</v>
       </c>
       <c r="T180" t="n">
-        <v>12346.21</v>
+        <v>11538.66</v>
       </c>
     </row>
     <row r="181">
@@ -14672,13 +14672,13 @@
         <v>0.3322</v>
       </c>
       <c r="K181" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L181" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M181" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N181" t="n">
         <v>25041.23</v>
@@ -14699,7 +14699,7 @@
         <v>0.0202</v>
       </c>
       <c r="T181" t="n">
-        <v>8509.84</v>
+        <v>9264.299999999999</v>
       </c>
     </row>
     <row r="182">
@@ -14738,10 +14738,10 @@
         <v>0.3568</v>
       </c>
       <c r="K182" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L182" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M182" t="n">
         <v>8</v>
@@ -14765,7 +14765,7 @@
         <v>0.0401</v>
       </c>
       <c r="T182" t="n">
-        <v>7528.71</v>
+        <v>4426.75</v>
       </c>
     </row>
     <row r="183">
@@ -14804,10 +14804,10 @@
         <v>0.4394</v>
       </c>
       <c r="K183" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L183" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M183" t="n">
         <v>5</v>
@@ -14831,7 +14831,7 @@
         <v>0.0435</v>
       </c>
       <c r="T183" t="n">
-        <v>14166.59</v>
+        <v>16852.19</v>
       </c>
     </row>
     <row r="184">
@@ -14870,13 +14870,13 @@
         <v>0.4433</v>
       </c>
       <c r="K184" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L184" t="n">
         <v>9</v>
       </c>
       <c r="M184" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N184" t="n">
         <v>2657.31</v>
@@ -14897,7 +14897,7 @@
         <v>0.0218</v>
       </c>
       <c r="T184" t="n">
-        <v>8422.610000000001</v>
+        <v>9679</v>
       </c>
     </row>
     <row r="185">
@@ -14936,13 +14936,13 @@
         <v>0.4248</v>
       </c>
       <c r="K185" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L185" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M185" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N185" t="n">
         <v>10494.51</v>
@@ -14963,7 +14963,7 @@
         <v>0.0122</v>
       </c>
       <c r="T185" t="n">
-        <v>12287.56</v>
+        <v>11759.16</v>
       </c>
     </row>
     <row r="186">
@@ -15002,10 +15002,10 @@
         <v>0.4026</v>
       </c>
       <c r="K186" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L186" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M186" t="n">
         <v>7</v>
@@ -15029,7 +15029,7 @@
         <v>0.0326</v>
       </c>
       <c r="T186" t="n">
-        <v>8369.07</v>
+        <v>7968.16</v>
       </c>
     </row>
     <row r="187">
@@ -15068,13 +15068,13 @@
         <v>0.2944</v>
       </c>
       <c r="K187" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L187" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M187" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N187" t="n">
         <v>11980.19</v>
@@ -15095,7 +15095,7 @@
         <v>0.0397</v>
       </c>
       <c r="T187" t="n">
-        <v>14770.4</v>
+        <v>14859.68</v>
       </c>
     </row>
     <row r="188">
@@ -15161,7 +15161,7 @@
         <v>0.0444</v>
       </c>
       <c r="T188" t="n">
-        <v>7877.44</v>
+        <v>6592.83</v>
       </c>
     </row>
     <row r="189">
@@ -15200,13 +15200,13 @@
         <v>0.4083</v>
       </c>
       <c r="K189" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L189" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M189" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N189" t="n">
         <v>15541.79</v>
@@ -15227,7 +15227,7 @@
         <v>0.0445</v>
       </c>
       <c r="T189" t="n">
-        <v>2726.67</v>
+        <v>4431.58</v>
       </c>
     </row>
     <row r="190">
@@ -15266,13 +15266,13 @@
         <v>0.3911</v>
       </c>
       <c r="K190" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L190" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M190" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N190" t="n">
         <v>20220.39</v>
@@ -15293,7 +15293,7 @@
         <v>0.0301</v>
       </c>
       <c r="T190" t="n">
-        <v>22189.31</v>
+        <v>20242.79</v>
       </c>
     </row>
     <row r="191">
@@ -15332,10 +15332,10 @@
         <v>0.3598</v>
       </c>
       <c r="K191" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M191" t="n">
         <v>13</v>
@@ -15359,7 +15359,7 @@
         <v>0.0162</v>
       </c>
       <c r="T191" t="n">
-        <v>30133.55</v>
+        <v>29884.24</v>
       </c>
     </row>
     <row r="192">
@@ -15401,10 +15401,10 @@
         <v>18</v>
       </c>
       <c r="L192" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M192" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N192" t="n">
         <v>5627.81</v>
@@ -15425,7 +15425,7 @@
         <v>0.0307</v>
       </c>
       <c r="T192" t="n">
-        <v>7610.96</v>
+        <v>9220.75</v>
       </c>
     </row>
     <row r="193">
@@ -15464,13 +15464,13 @@
         <v>0.3693</v>
       </c>
       <c r="K193" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L193" t="n">
         <v>8</v>
       </c>
       <c r="M193" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N193" t="n">
         <v>13846.99</v>
@@ -15491,7 +15491,7 @@
         <v>0.0419</v>
       </c>
       <c r="T193" t="n">
-        <v>12580.38</v>
+        <v>12746.12</v>
       </c>
     </row>
     <row r="194">
@@ -15530,13 +15530,13 @@
         <v>0.2981</v>
       </c>
       <c r="K194" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L194" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M194" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N194" t="n">
         <v>3594.91</v>
@@ -15557,7 +15557,7 @@
         <v>0.0147</v>
       </c>
       <c r="T194" t="n">
-        <v>9150.360000000001</v>
+        <v>7612.52</v>
       </c>
     </row>
     <row r="195">
@@ -15596,10 +15596,10 @@
         <v>0.3552</v>
       </c>
       <c r="K195" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L195" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M195" t="n">
         <v>6</v>
@@ -15623,7 +15623,7 @@
         <v>0.0444</v>
       </c>
       <c r="T195" t="n">
-        <v>8998.98</v>
+        <v>12306.1</v>
       </c>
     </row>
     <row r="196">
@@ -15662,10 +15662,10 @@
         <v>0.3771</v>
       </c>
       <c r="K196" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L196" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M196" t="n">
         <v>9</v>
@@ -15689,7 +15689,7 @@
         <v>0.0281</v>
       </c>
       <c r="T196" t="n">
-        <v>14626.81</v>
+        <v>12285.12</v>
       </c>
     </row>
     <row r="197">
@@ -15728,10 +15728,10 @@
         <v>0.3966</v>
       </c>
       <c r="K197" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L197" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M197" t="n">
         <v>6</v>
@@ -15755,7 +15755,7 @@
         <v>0.0086</v>
       </c>
       <c r="T197" t="n">
-        <v>5578.96</v>
+        <v>5908.55</v>
       </c>
     </row>
     <row r="198">
@@ -15794,10 +15794,10 @@
         <v>0.3592</v>
       </c>
       <c r="K198" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L198" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M198" t="n">
         <v>7</v>
@@ -15821,7 +15821,7 @@
         <v>0.046</v>
       </c>
       <c r="T198" t="n">
-        <v>9391.33</v>
+        <v>9253.370000000001</v>
       </c>
     </row>
     <row r="199">
@@ -15860,13 +15860,13 @@
         <v>0.3763</v>
       </c>
       <c r="K199" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L199" t="n">
         <v>6</v>
       </c>
       <c r="M199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N199" t="n">
         <v>8321.540000000001</v>
@@ -15887,7 +15887,7 @@
         <v>0.0216</v>
       </c>
       <c r="T199" t="n">
-        <v>3579.82</v>
+        <v>3960.6</v>
       </c>
     </row>
     <row r="200">
@@ -15926,13 +15926,13 @@
         <v>0.2899</v>
       </c>
       <c r="K200" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L200" t="n">
         <v>3</v>
       </c>
       <c r="M200" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N200" t="n">
         <v>8165.32</v>
@@ -15953,7 +15953,7 @@
         <v>0.0401</v>
       </c>
       <c r="T200" t="n">
-        <v>20948.71</v>
+        <v>8258.02</v>
       </c>
     </row>
     <row r="201">
@@ -15992,13 +15992,13 @@
         <v>0.3007</v>
       </c>
       <c r="K201" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L201" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M201" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N201" t="n">
         <v>7276.24</v>
@@ -16019,7 +16019,7 @@
         <v>0.044</v>
       </c>
       <c r="T201" t="n">
-        <v>12382.81</v>
+        <v>19085.92</v>
       </c>
     </row>
     <row r="202">
@@ -16058,13 +16058,13 @@
         <v>0.3164</v>
       </c>
       <c r="K202" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L202" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M202" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N202" t="n">
         <v>7190.72</v>
@@ -16085,7 +16085,7 @@
         <v>0.0414</v>
       </c>
       <c r="T202" t="n">
-        <v>8046.86</v>
+        <v>23494.22</v>
       </c>
     </row>
     <row r="203">
@@ -16124,13 +16124,13 @@
         <v>0.3273</v>
       </c>
       <c r="K203" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L203" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M203" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N203" t="n">
         <v>8233.940000000001</v>
@@ -16151,7 +16151,7 @@
         <v>0.0097</v>
       </c>
       <c r="T203" t="n">
-        <v>7949.34</v>
+        <v>4237.62</v>
       </c>
     </row>
     <row r="204">
@@ -16190,13 +16190,13 @@
         <v>0.4102</v>
       </c>
       <c r="K204" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L204" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M204" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N204" t="n">
         <v>3399.88</v>
@@ -16217,7 +16217,7 @@
         <v>0.0117</v>
       </c>
       <c r="T204" t="n">
-        <v>12113.09</v>
+        <v>6292.01</v>
       </c>
     </row>
     <row r="205">
@@ -16256,13 +16256,13 @@
         <v>0.3142</v>
       </c>
       <c r="K205" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L205" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M205" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N205" t="n">
         <v>6471.44</v>
@@ -16283,7 +16283,7 @@
         <v>0.0097</v>
       </c>
       <c r="T205" t="n">
-        <v>34798.02</v>
+        <v>34871.04</v>
       </c>
     </row>
     <row r="206">
@@ -16322,10 +16322,10 @@
         <v>0.3203</v>
       </c>
       <c r="K206" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L206" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M206" t="n">
         <v>12</v>
@@ -16349,7 +16349,7 @@
         <v>0.0401</v>
       </c>
       <c r="T206" t="n">
-        <v>11018.34</v>
+        <v>15211.52</v>
       </c>
     </row>
     <row r="207">
@@ -16388,13 +16388,13 @@
         <v>0.446</v>
       </c>
       <c r="K207" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L207" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M207" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N207" t="n">
         <v>3848.71</v>
@@ -16415,7 +16415,7 @@
         <v>0.0497</v>
       </c>
       <c r="T207" t="n">
-        <v>6108.76</v>
+        <v>8270.129999999999</v>
       </c>
     </row>
     <row r="208">
@@ -16454,10 +16454,10 @@
         <v>0.3859</v>
       </c>
       <c r="K208" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L208" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M208" t="n">
         <v>6</v>
@@ -16481,7 +16481,7 @@
         <v>0.0361</v>
       </c>
       <c r="T208" t="n">
-        <v>13513.74</v>
+        <v>13951.65</v>
       </c>
     </row>
     <row r="209">
@@ -16523,10 +16523,10 @@
         <v>14</v>
       </c>
       <c r="L209" t="n">
+        <v>6</v>
+      </c>
+      <c r="M209" t="n">
         <v>8</v>
-      </c>
-      <c r="M209" t="n">
-        <v>6</v>
       </c>
       <c r="N209" t="n">
         <v>6179.81</v>
@@ -16547,7 +16547,7 @@
         <v>0.0368</v>
       </c>
       <c r="T209" t="n">
-        <v>7137.12</v>
+        <v>5282.53</v>
       </c>
     </row>
     <row r="210">
@@ -16586,13 +16586,13 @@
         <v>0.3858</v>
       </c>
       <c r="K210" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L210" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M210" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N210" t="n">
         <v>9985.82</v>
@@ -16613,7 +16613,7 @@
         <v>0.0183</v>
       </c>
       <c r="T210" t="n">
-        <v>5422.95</v>
+        <v>2800.2</v>
       </c>
     </row>
     <row r="211">
@@ -16652,13 +16652,13 @@
         <v>0.3296</v>
       </c>
       <c r="K211" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="L211" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M211" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N211" t="n">
         <v>15589.92</v>
@@ -16679,7 +16679,7 @@
         <v>0.0169</v>
       </c>
       <c r="T211" t="n">
-        <v>10849.35</v>
+        <v>8534.23</v>
       </c>
     </row>
     <row r="212">
@@ -16718,13 +16718,13 @@
         <v>0.3623</v>
       </c>
       <c r="K212" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L212" t="n">
         <v>6</v>
       </c>
       <c r="M212" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N212" t="n">
         <v>8248.389999999999</v>
@@ -16745,7 +16745,7 @@
         <v>0.019</v>
       </c>
       <c r="T212" t="n">
-        <v>3843.94</v>
+        <v>3657.14</v>
       </c>
     </row>
     <row r="213">
@@ -16784,10 +16784,10 @@
         <v>0.4333</v>
       </c>
       <c r="K213" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L213" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M213" t="n">
         <v>5</v>
@@ -16811,7 +16811,7 @@
         <v>0.0449</v>
       </c>
       <c r="T213" t="n">
-        <v>7330.85</v>
+        <v>7455.75</v>
       </c>
     </row>
     <row r="214">
@@ -16850,13 +16850,13 @@
         <v>0.339</v>
       </c>
       <c r="K214" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L214" t="n">
         <v>4</v>
       </c>
       <c r="M214" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N214" t="n">
         <v>14256.89</v>
@@ -16877,7 +16877,7 @@
         <v>0.0457</v>
       </c>
       <c r="T214" t="n">
-        <v>14297.93</v>
+        <v>12944.56</v>
       </c>
     </row>
     <row r="215">
@@ -16916,10 +16916,10 @@
         <v>0.263</v>
       </c>
       <c r="K215" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M215" t="n">
         <v>5</v>
@@ -16943,7 +16943,7 @@
         <v>0.0384</v>
       </c>
       <c r="T215" t="n">
-        <v>2339.07</v>
+        <v>3045.66</v>
       </c>
     </row>
     <row r="216">
@@ -16982,10 +16982,10 @@
         <v>0.3775</v>
       </c>
       <c r="K216" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L216" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M216" t="n">
         <v>6</v>
@@ -17009,7 +17009,7 @@
         <v>0.0178</v>
       </c>
       <c r="T216" t="n">
-        <v>12260.37</v>
+        <v>13898.27</v>
       </c>
     </row>
     <row r="217">
@@ -17048,10 +17048,10 @@
         <v>0.4081</v>
       </c>
       <c r="K217" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L217" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M217" t="n">
         <v>4</v>
@@ -17075,7 +17075,7 @@
         <v>0.0344</v>
       </c>
       <c r="T217" t="n">
-        <v>8298.66</v>
+        <v>7369.44</v>
       </c>
     </row>
     <row r="218">
@@ -17114,13 +17114,13 @@
         <v>0.2672</v>
       </c>
       <c r="K218" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L218" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M218" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N218" t="n">
         <v>17081.42</v>
@@ -17141,7 +17141,7 @@
         <v>0.0428</v>
       </c>
       <c r="T218" t="n">
-        <v>19777.25</v>
+        <v>18865.24</v>
       </c>
     </row>
     <row r="219">
@@ -17180,10 +17180,10 @@
         <v>0.4147</v>
       </c>
       <c r="K219" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L219" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M219" t="n">
         <v>7</v>
@@ -17207,7 +17207,7 @@
         <v>0.0249</v>
       </c>
       <c r="T219" t="n">
-        <v>1738</v>
+        <v>4712.54</v>
       </c>
     </row>
     <row r="220">
@@ -17312,13 +17312,13 @@
         <v>0.3365</v>
       </c>
       <c r="K221" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L221" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M221" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N221" t="n">
         <v>24385.06</v>
@@ -17339,7 +17339,7 @@
         <v>0.0193</v>
       </c>
       <c r="T221" t="n">
-        <v>12349.08</v>
+        <v>10159.81</v>
       </c>
     </row>
     <row r="222">
@@ -17378,13 +17378,13 @@
         <v>0.3145</v>
       </c>
       <c r="K222" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L222" t="n">
         <v>6</v>
       </c>
       <c r="M222" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N222" t="n">
         <v>6472.98</v>
@@ -17405,7 +17405,7 @@
         <v>0.0207</v>
       </c>
       <c r="T222" t="n">
-        <v>8985.18</v>
+        <v>8952.58</v>
       </c>
     </row>
     <row r="223">
@@ -17444,13 +17444,13 @@
         <v>0.3001</v>
       </c>
       <c r="K223" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L223" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M223" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N223" t="n">
         <v>24983.26</v>
@@ -17471,7 +17471,7 @@
         <v>0.0234</v>
       </c>
       <c r="T223" t="n">
-        <v>4235.89</v>
+        <v>4395.23</v>
       </c>
     </row>
     <row r="224">
@@ -17513,10 +17513,10 @@
         <v>15</v>
       </c>
       <c r="L224" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M224" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N224" t="n">
         <v>10293.06</v>
@@ -17537,7 +17537,7 @@
         <v>0.0337</v>
       </c>
       <c r="T224" t="n">
-        <v>9354.860000000001</v>
+        <v>6125.77</v>
       </c>
     </row>
     <row r="225">
@@ -17576,13 +17576,13 @@
         <v>0.4185</v>
       </c>
       <c r="K225" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L225" t="n">
         <v>6</v>
       </c>
       <c r="M225" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N225" t="n">
         <v>4112.99</v>
@@ -17603,7 +17603,7 @@
         <v>0.0242</v>
       </c>
       <c r="T225" t="n">
-        <v>11561.79</v>
+        <v>13960.33</v>
       </c>
     </row>
     <row r="226">
@@ -17642,13 +17642,13 @@
         <v>0.3654</v>
       </c>
       <c r="K226" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L226" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M226" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N226" t="n">
         <v>6720.17</v>
@@ -17669,7 +17669,7 @@
         <v>0.0486</v>
       </c>
       <c r="T226" t="n">
-        <v>5247.23</v>
+        <v>4810.99</v>
       </c>
     </row>
     <row r="227">
@@ -17711,10 +17711,10 @@
         <v>15</v>
       </c>
       <c r="L227" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M227" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N227" t="n">
         <v>9706.209999999999</v>
@@ -17735,7 +17735,7 @@
         <v>0.0323</v>
       </c>
       <c r="T227" t="n">
-        <v>26450.2</v>
+        <v>27751.4</v>
       </c>
     </row>
     <row r="228">
@@ -17774,13 +17774,13 @@
         <v>0.3095</v>
       </c>
       <c r="K228" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L228" t="n">
         <v>7</v>
       </c>
       <c r="M228" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N228" t="n">
         <v>5029.57</v>
@@ -17801,7 +17801,7 @@
         <v>0.0378</v>
       </c>
       <c r="T228" t="n">
-        <v>21761.47</v>
+        <v>21692.96</v>
       </c>
     </row>
     <row r="229">
@@ -17867,7 +17867,7 @@
         <v>0.0364</v>
       </c>
       <c r="T229" t="n">
-        <v>15644.57</v>
+        <v>15678.67</v>
       </c>
     </row>
     <row r="230">
@@ -17906,13 +17906,13 @@
         <v>0.3241</v>
       </c>
       <c r="K230" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L230" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M230" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N230" t="n">
         <v>27917.33</v>
@@ -17933,7 +17933,7 @@
         <v>0.0467</v>
       </c>
       <c r="T230" t="n">
-        <v>8558.4</v>
+        <v>7109.2</v>
       </c>
     </row>
     <row r="231">
@@ -17999,7 +17999,7 @@
         <v>0.0328</v>
       </c>
       <c r="T231" t="n">
-        <v>3955.35</v>
+        <v>5256.37</v>
       </c>
     </row>
     <row r="232">
@@ -18038,10 +18038,10 @@
         <v>0.2819</v>
       </c>
       <c r="K232" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L232" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M232" t="n">
         <v>8</v>
@@ -18065,7 +18065,7 @@
         <v>0.0388</v>
       </c>
       <c r="T232" t="n">
-        <v>4569.6</v>
+        <v>5276.61</v>
       </c>
     </row>
     <row r="233">
@@ -18104,13 +18104,13 @@
         <v>0.3529</v>
       </c>
       <c r="K233" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L233" t="n">
         <v>2</v>
       </c>
       <c r="M233" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N233" t="n">
         <v>13503.96</v>
@@ -18131,7 +18131,7 @@
         <v>0.0493</v>
       </c>
       <c r="T233" t="n">
-        <v>6351.94</v>
+        <v>9705.379999999999</v>
       </c>
     </row>
     <row r="234">
@@ -18170,13 +18170,13 @@
         <v>0.4433</v>
       </c>
       <c r="K234" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L234" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M234" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N234" t="n">
         <v>18500.48</v>
@@ -18197,7 +18197,7 @@
         <v>0.046</v>
       </c>
       <c r="T234" t="n">
-        <v>13482.82</v>
+        <v>10572.28</v>
       </c>
     </row>
     <row r="235">
@@ -18236,13 +18236,13 @@
         <v>0.3809</v>
       </c>
       <c r="K235" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L235" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M235" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N235" t="n">
         <v>4223.82</v>
@@ -18263,7 +18263,7 @@
         <v>0.009599999999999999</v>
       </c>
       <c r="T235" t="n">
-        <v>25294.14</v>
+        <v>24292.41</v>
       </c>
     </row>
     <row r="236">
@@ -18329,7 +18329,7 @@
         <v>0.0159</v>
       </c>
       <c r="T236" t="n">
-        <v>9748.07</v>
+        <v>21765.79</v>
       </c>
     </row>
     <row r="237">
@@ -18368,13 +18368,13 @@
         <v>0.2647</v>
       </c>
       <c r="K237" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L237" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M237" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N237" t="n">
         <v>3066.79</v>
@@ -18395,7 +18395,7 @@
         <v>0.0182</v>
       </c>
       <c r="T237" t="n">
-        <v>23215.12</v>
+        <v>12359.96</v>
       </c>
     </row>
     <row r="238">
@@ -18434,13 +18434,13 @@
         <v>0.2738</v>
       </c>
       <c r="K238" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L238" t="n">
         <v>8</v>
       </c>
       <c r="M238" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N238" t="n">
         <v>22114.27</v>
@@ -18461,7 +18461,7 @@
         <v>0.0083</v>
       </c>
       <c r="T238" t="n">
-        <v>17751.7</v>
+        <v>17725.3</v>
       </c>
     </row>
     <row r="239">
@@ -18527,7 +18527,7 @@
         <v>0.022</v>
       </c>
       <c r="T239" t="n">
-        <v>14433.87</v>
+        <v>14338.89</v>
       </c>
     </row>
     <row r="240">
@@ -18566,13 +18566,13 @@
         <v>0.3166</v>
       </c>
       <c r="K240" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L240" t="n">
+        <v>8</v>
+      </c>
+      <c r="M240" t="n">
         <v>10</v>
-      </c>
-      <c r="M240" t="n">
-        <v>12</v>
       </c>
       <c r="N240" t="n">
         <v>21917.12</v>
@@ -18593,7 +18593,7 @@
         <v>0.04</v>
       </c>
       <c r="T240" t="n">
-        <v>14519.46</v>
+        <v>12660.8</v>
       </c>
     </row>
     <row r="241">
@@ -18635,10 +18635,10 @@
         <v>18</v>
       </c>
       <c r="L241" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M241" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N241" t="n">
         <v>5004.21</v>
@@ -18659,7 +18659,7 @@
         <v>0.0372</v>
       </c>
       <c r="T241" t="n">
-        <v>9481.360000000001</v>
+        <v>10298.84</v>
       </c>
     </row>
     <row r="242">
@@ -18698,10 +18698,10 @@
         <v>0.3565</v>
       </c>
       <c r="K242" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L242" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M242" t="n">
         <v>4</v>
@@ -18725,7 +18725,7 @@
         <v>0.0463</v>
       </c>
       <c r="T242" t="n">
-        <v>9045.780000000001</v>
+        <v>9350.58</v>
       </c>
     </row>
     <row r="243">
@@ -18764,13 +18764,13 @@
         <v>0.446</v>
       </c>
       <c r="K243" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L243" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M243" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N243" t="n">
         <v>25579.97</v>
@@ -18791,7 +18791,7 @@
         <v>0.0388</v>
       </c>
       <c r="T243" t="n">
-        <v>10848.64</v>
+        <v>9278.969999999999</v>
       </c>
     </row>
     <row r="244">
@@ -18830,13 +18830,13 @@
         <v>0.3449</v>
       </c>
       <c r="K244" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L244" t="n">
         <v>3</v>
       </c>
       <c r="M244" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N244" t="n">
         <v>28869.04</v>
@@ -18857,7 +18857,7 @@
         <v>0.0357</v>
       </c>
       <c r="T244" t="n">
-        <v>5490.4</v>
+        <v>7681.06</v>
       </c>
     </row>
     <row r="245">
@@ -18896,13 +18896,13 @@
         <v>0.3667</v>
       </c>
       <c r="K245" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L245" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M245" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N245" t="n">
         <v>23811.17</v>
@@ -18923,7 +18923,7 @@
         <v>0.0449</v>
       </c>
       <c r="T245" t="n">
-        <v>21188.98</v>
+        <v>21063.23</v>
       </c>
     </row>
     <row r="246">
@@ -18962,13 +18962,13 @@
         <v>0.3861</v>
       </c>
       <c r="K246" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L246" t="n">
+        <v>2</v>
+      </c>
+      <c r="M246" t="n">
         <v>4</v>
-      </c>
-      <c r="M246" t="n">
-        <v>3</v>
       </c>
       <c r="N246" t="n">
         <v>10233.28</v>
@@ -18989,7 +18989,7 @@
         <v>0.0318</v>
       </c>
       <c r="T246" t="n">
-        <v>2704.34</v>
+        <v>1746.78</v>
       </c>
     </row>
     <row r="247">
@@ -19028,13 +19028,13 @@
         <v>0.2803</v>
       </c>
       <c r="K247" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L247" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M247" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N247" t="n">
         <v>37710.42</v>
@@ -19055,7 +19055,7 @@
         <v>0.0411</v>
       </c>
       <c r="T247" t="n">
-        <v>8081.16</v>
+        <v>8238.68</v>
       </c>
     </row>
     <row r="248">
@@ -19094,10 +19094,10 @@
         <v>0.2625</v>
       </c>
       <c r="K248" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L248" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M248" t="n">
         <v>9</v>
@@ -19121,7 +19121,7 @@
         <v>0.0488</v>
       </c>
       <c r="T248" t="n">
-        <v>17559.45</v>
+        <v>10968.31</v>
       </c>
     </row>
     <row r="249">
@@ -19160,13 +19160,13 @@
         <v>0.3128</v>
       </c>
       <c r="K249" t="n">
+        <v>17</v>
+      </c>
+      <c r="L249" t="n">
         <v>10</v>
       </c>
-      <c r="L249" t="n">
+      <c r="M249" t="n">
         <v>7</v>
-      </c>
-      <c r="M249" t="n">
-        <v>3</v>
       </c>
       <c r="N249" t="n">
         <v>6701.48</v>
@@ -19187,7 +19187,7 @@
         <v>0.0066</v>
       </c>
       <c r="T249" t="n">
-        <v>10710.02</v>
+        <v>13716.51</v>
       </c>
     </row>
     <row r="250">
@@ -19226,13 +19226,13 @@
         <v>0.3942</v>
       </c>
       <c r="K250" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L250" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M250" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N250" t="n">
         <v>13703.77</v>
@@ -19253,7 +19253,7 @@
         <v>0.0391</v>
       </c>
       <c r="T250" t="n">
-        <v>29110.33</v>
+        <v>34346.42</v>
       </c>
     </row>
     <row r="251">
@@ -19292,13 +19292,13 @@
         <v>0.3616</v>
       </c>
       <c r="K251" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L251" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M251" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N251" t="n">
         <v>20177.65</v>
@@ -19319,7 +19319,7 @@
         <v>0.0353</v>
       </c>
       <c r="T251" t="n">
-        <v>2429.22</v>
+        <v>2559.23</v>
       </c>
     </row>
     <row r="252">
@@ -19358,13 +19358,13 @@
         <v>0.391</v>
       </c>
       <c r="K252" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L252" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M252" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N252" t="n">
         <v>19143.68</v>
@@ -19385,7 +19385,7 @@
         <v>0.0169</v>
       </c>
       <c r="T252" t="n">
-        <v>3527.27</v>
+        <v>3626.07</v>
       </c>
     </row>
     <row r="253">
@@ -19424,10 +19424,10 @@
         <v>0.2744</v>
       </c>
       <c r="K253" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L253" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M253" t="n">
         <v>3</v>
@@ -19451,7 +19451,7 @@
         <v>0.0064</v>
       </c>
       <c r="T253" t="n">
-        <v>9154.200000000001</v>
+        <v>7273.95</v>
       </c>
     </row>
   </sheetData>
@@ -67979,7 +67979,7 @@
         <v>2439.7</v>
       </c>
       <c r="G2" t="n">
-        <v>285.85</v>
+        <v>280.49</v>
       </c>
       <c r="H2" t="n">
         <v>2877.56</v>
@@ -68012,7 +68012,7 @@
         <v>2233.82</v>
       </c>
       <c r="G3" t="n">
-        <v>276.55</v>
+        <v>317.38</v>
       </c>
       <c r="H3" t="n">
         <v>3379.73</v>
@@ -68078,7 +68078,7 @@
         <v>2570.55</v>
       </c>
       <c r="G5" t="n">
-        <v>235.56</v>
+        <v>240.64</v>
       </c>
       <c r="H5" t="n">
         <v>2919.02</v>
@@ -68111,7 +68111,7 @@
         <v>3254.51</v>
       </c>
       <c r="G6" t="n">
-        <v>234.56</v>
+        <v>223.93</v>
       </c>
       <c r="H6" t="n">
         <v>963.41</v>
@@ -68144,7 +68144,7 @@
         <v>3063.51</v>
       </c>
       <c r="G7" t="n">
-        <v>277.74</v>
+        <v>257.01</v>
       </c>
       <c r="H7" t="n">
         <v>1125.5</v>
@@ -68177,7 +68177,7 @@
         <v>1652.16</v>
       </c>
       <c r="G8" t="n">
-        <v>268.58</v>
+        <v>272.19</v>
       </c>
       <c r="H8" t="n">
         <v>1609.29</v>
@@ -68210,7 +68210,7 @@
         <v>1225.43</v>
       </c>
       <c r="G9" t="n">
-        <v>287.82</v>
+        <v>322.95</v>
       </c>
       <c r="H9" t="n">
         <v>765.5700000000001</v>
@@ -68243,7 +68243,7 @@
         <v>1211.57</v>
       </c>
       <c r="G10" t="n">
-        <v>261.92</v>
+        <v>258.05</v>
       </c>
       <c r="H10" t="n">
         <v>1269.36</v>
@@ -68276,7 +68276,7 @@
         <v>1899.82</v>
       </c>
       <c r="G11" t="n">
-        <v>330.54</v>
+        <v>320.1</v>
       </c>
       <c r="H11" t="n">
         <v>1367.1</v>
@@ -68309,7 +68309,7 @@
         <v>2015.99</v>
       </c>
       <c r="G12" t="n">
-        <v>237.78</v>
+        <v>234.64</v>
       </c>
       <c r="H12" t="n">
         <v>1217.86</v>
@@ -68342,7 +68342,7 @@
         <v>2197.15</v>
       </c>
       <c r="G13" t="n">
-        <v>237.34</v>
+        <v>228.01</v>
       </c>
       <c r="H13" t="n">
         <v>1835.28</v>
@@ -68408,7 +68408,7 @@
         <v>2792.28</v>
       </c>
       <c r="G15" t="n">
-        <v>254.37</v>
+        <v>251.17</v>
       </c>
       <c r="H15" t="n">
         <v>3755.47</v>
@@ -68441,7 +68441,7 @@
         <v>2261.63</v>
       </c>
       <c r="G16" t="n">
-        <v>263.29</v>
+        <v>258.42</v>
       </c>
       <c r="H16" t="n">
         <v>2645.7</v>
@@ -68507,7 +68507,7 @@
         <v>1831.14</v>
       </c>
       <c r="G18" t="n">
-        <v>231.01</v>
+        <v>234.88</v>
       </c>
       <c r="H18" t="n">
         <v>1581.22</v>
@@ -68540,7 +68540,7 @@
         <v>2596.84</v>
       </c>
       <c r="G19" t="n">
-        <v>246.91</v>
+        <v>251.18</v>
       </c>
       <c r="H19" t="n">
         <v>3112.2</v>
@@ -68573,7 +68573,7 @@
         <v>2159.44</v>
       </c>
       <c r="G20" t="n">
-        <v>255.95</v>
+        <v>248.49</v>
       </c>
       <c r="H20" t="n">
         <v>831.05</v>
@@ -68606,7 +68606,7 @@
         <v>1694.46</v>
       </c>
       <c r="G21" t="n">
-        <v>255.22</v>
+        <v>267.97</v>
       </c>
       <c r="H21" t="n">
         <v>689.0700000000001</v>
@@ -68639,7 +68639,7 @@
         <v>2217.53</v>
       </c>
       <c r="G22" t="n">
-        <v>292.02</v>
+        <v>308.26</v>
       </c>
       <c r="H22" t="n">
         <v>746.5599999999999</v>
@@ -68672,7 +68672,7 @@
         <v>2180.55</v>
       </c>
       <c r="G23" t="n">
-        <v>243.84</v>
+        <v>238.97</v>
       </c>
       <c r="H23" t="n">
         <v>1757.93</v>
@@ -68705,7 +68705,7 @@
         <v>1555.87</v>
       </c>
       <c r="G24" t="n">
-        <v>238.86</v>
+        <v>227.76</v>
       </c>
       <c r="H24" t="n">
         <v>1703.79</v>
@@ -68738,7 +68738,7 @@
         <v>1865.24</v>
       </c>
       <c r="G25" t="n">
-        <v>231.63</v>
+        <v>234.79</v>
       </c>
       <c r="H25" t="n">
         <v>1022.34</v>
@@ -68804,7 +68804,7 @@
         <v>2064.44</v>
       </c>
       <c r="G27" t="n">
-        <v>291.1</v>
+        <v>339.33</v>
       </c>
       <c r="H27" t="n">
         <v>2259.9</v>
@@ -68837,7 +68837,7 @@
         <v>1508.63</v>
       </c>
       <c r="G28" t="n">
-        <v>289.35</v>
+        <v>277.44</v>
       </c>
       <c r="H28" t="n">
         <v>1911.45</v>
@@ -68870,7 +68870,7 @@
         <v>1584.24</v>
       </c>
       <c r="G29" t="n">
-        <v>266.26</v>
+        <v>253.01</v>
       </c>
       <c r="H29" t="n">
         <v>2037.35</v>
@@ -68903,7 +68903,7 @@
         <v>1480.62</v>
       </c>
       <c r="G30" t="n">
-        <v>247.44</v>
+        <v>240.15</v>
       </c>
       <c r="H30" t="n">
         <v>1050.74</v>
@@ -68936,7 +68936,7 @@
         <v>1483.52</v>
       </c>
       <c r="G31" t="n">
-        <v>240.2</v>
+        <v>234.02</v>
       </c>
       <c r="H31" t="n">
         <v>2306.57</v>
@@ -68969,7 +68969,7 @@
         <v>2271.54</v>
       </c>
       <c r="G32" t="n">
-        <v>270.37</v>
+        <v>265.68</v>
       </c>
       <c r="H32" t="n">
         <v>2264.7</v>
@@ -69002,7 +69002,7 @@
         <v>2184.79</v>
       </c>
       <c r="G33" t="n">
-        <v>225.89</v>
+        <v>249.2</v>
       </c>
       <c r="H33" t="n">
         <v>1476.6</v>
@@ -69035,7 +69035,7 @@
         <v>1605.64</v>
       </c>
       <c r="G34" t="n">
-        <v>273.32</v>
+        <v>257.38</v>
       </c>
       <c r="H34" t="n">
         <v>2588.01</v>
@@ -69101,7 +69101,7 @@
         <v>1627.99</v>
       </c>
       <c r="G36" t="n">
-        <v>285.29</v>
+        <v>268.23</v>
       </c>
       <c r="H36" t="n">
         <v>1625.68</v>
@@ -69200,7 +69200,7 @@
         <v>2371.89</v>
       </c>
       <c r="G39" t="n">
-        <v>241.67</v>
+        <v>259.03</v>
       </c>
       <c r="H39" t="n">
         <v>1093.01</v>
@@ -69233,7 +69233,7 @@
         <v>2260.45</v>
       </c>
       <c r="G40" t="n">
-        <v>255.93</v>
+        <v>247.54</v>
       </c>
       <c r="H40" t="n">
         <v>2343.36</v>
@@ -69266,7 +69266,7 @@
         <v>2942.96</v>
       </c>
       <c r="G41" t="n">
-        <v>246.73</v>
+        <v>237.97</v>
       </c>
       <c r="H41" t="n">
         <v>1830.08</v>
@@ -69299,7 +69299,7 @@
         <v>2631.71</v>
       </c>
       <c r="G42" t="n">
-        <v>245.53</v>
+        <v>249.03</v>
       </c>
       <c r="H42" t="n">
         <v>1442.66</v>
@@ -69398,7 +69398,7 @@
         <v>1847.47</v>
       </c>
       <c r="G45" t="n">
-        <v>306.75</v>
+        <v>342.34</v>
       </c>
       <c r="H45" t="n">
         <v>3904.3</v>
@@ -69431,7 +69431,7 @@
         <v>1702.3</v>
       </c>
       <c r="G46" t="n">
-        <v>349.79</v>
+        <v>379.74</v>
       </c>
       <c r="H46" t="n">
         <v>3311.43</v>
@@ -69464,7 +69464,7 @@
         <v>2121.71</v>
       </c>
       <c r="G47" t="n">
-        <v>278.13</v>
+        <v>243.95</v>
       </c>
       <c r="H47" t="n">
         <v>3885.01</v>
@@ -69497,7 +69497,7 @@
         <v>1882.12</v>
       </c>
       <c r="G48" t="n">
-        <v>313.57</v>
+        <v>293.82</v>
       </c>
       <c r="H48" t="n">
         <v>2743.46</v>
@@ -69563,7 +69563,7 @@
         <v>1634.67</v>
       </c>
       <c r="G50" t="n">
-        <v>276.73</v>
+        <v>272.21</v>
       </c>
       <c r="H50" t="n">
         <v>2125.94</v>
@@ -69596,7 +69596,7 @@
         <v>2029.16</v>
       </c>
       <c r="G51" t="n">
-        <v>246.2</v>
+        <v>258.8</v>
       </c>
       <c r="H51" t="n">
         <v>1633.04</v>
@@ -69629,7 +69629,7 @@
         <v>1883.59</v>
       </c>
       <c r="G52" t="n">
-        <v>263.69</v>
+        <v>259.95</v>
       </c>
       <c r="H52" t="n">
         <v>1679.17</v>
@@ -69662,7 +69662,7 @@
         <v>2539.44</v>
       </c>
       <c r="G53" t="n">
-        <v>232.74</v>
+        <v>235.26</v>
       </c>
       <c r="H53" t="n">
         <v>2301.72</v>
@@ -69695,7 +69695,7 @@
         <v>2087.12</v>
       </c>
       <c r="G54" t="n">
-        <v>226.35</v>
+        <v>223.42</v>
       </c>
       <c r="H54" t="n">
         <v>3372.99</v>
@@ -69728,7 +69728,7 @@
         <v>2314.53</v>
       </c>
       <c r="G55" t="n">
-        <v>238.79</v>
+        <v>233.25</v>
       </c>
       <c r="H55" t="n">
         <v>2677.89</v>
@@ -69761,7 +69761,7 @@
         <v>2708.27</v>
       </c>
       <c r="G56" t="n">
-        <v>261.35</v>
+        <v>252.58</v>
       </c>
       <c r="H56" t="n">
         <v>1047.79</v>
@@ -69794,7 +69794,7 @@
         <v>3278.47</v>
       </c>
       <c r="G57" t="n">
-        <v>238.11</v>
+        <v>259.89</v>
       </c>
       <c r="H57" t="n">
         <v>2543.22</v>
@@ -69860,7 +69860,7 @@
         <v>2674.4</v>
       </c>
       <c r="G59" t="n">
-        <v>279.68</v>
+        <v>274.99</v>
       </c>
       <c r="H59" t="n">
         <v>1346.12</v>
@@ -69893,7 +69893,7 @@
         <v>3125.63</v>
       </c>
       <c r="G60" t="n">
-        <v>229.16</v>
+        <v>234.02</v>
       </c>
       <c r="H60" t="n">
         <v>2303.95</v>
@@ -69926,7 +69926,7 @@
         <v>2853.33</v>
       </c>
       <c r="G61" t="n">
-        <v>279.25</v>
+        <v>268.68</v>
       </c>
       <c r="H61" t="n">
         <v>2837.38</v>
@@ -69959,7 +69959,7 @@
         <v>2362.6</v>
       </c>
       <c r="G62" t="n">
-        <v>251.15</v>
+        <v>246.89</v>
       </c>
       <c r="H62" t="n">
         <v>3197.32</v>
@@ -69992,7 +69992,7 @@
         <v>2828.81</v>
       </c>
       <c r="G63" t="n">
-        <v>238.75</v>
+        <v>241.98</v>
       </c>
       <c r="H63" t="n">
         <v>4271.29</v>
@@ -70025,7 +70025,7 @@
         <v>2299.23</v>
       </c>
       <c r="G64" t="n">
-        <v>252.18</v>
+        <v>244.35</v>
       </c>
       <c r="H64" t="n">
         <v>1669.96</v>
@@ -70058,7 +70058,7 @@
         <v>2303.63</v>
       </c>
       <c r="G65" t="n">
-        <v>263.64</v>
+        <v>254.55</v>
       </c>
       <c r="H65" t="n">
         <v>1918.39</v>
@@ -70091,7 +70091,7 @@
         <v>2986.99</v>
       </c>
       <c r="G66" t="n">
-        <v>239.99</v>
+        <v>264.98</v>
       </c>
       <c r="H66" t="n">
         <v>1228.06</v>
@@ -70157,7 +70157,7 @@
         <v>1553.71</v>
       </c>
       <c r="G68" t="n">
-        <v>259.47</v>
+        <v>254.06</v>
       </c>
       <c r="H68" t="n">
         <v>1408.6</v>
@@ -70190,7 +70190,7 @@
         <v>1533.29</v>
       </c>
       <c r="G69" t="n">
-        <v>308.5</v>
+        <v>331.35</v>
       </c>
       <c r="H69" t="n">
         <v>865.7</v>
@@ -70223,7 +70223,7 @@
         <v>1615.05</v>
       </c>
       <c r="G70" t="n">
-        <v>235.91</v>
+        <v>228.21</v>
       </c>
       <c r="H70" t="n">
         <v>879.24</v>
@@ -70256,7 +70256,7 @@
         <v>1936.26</v>
       </c>
       <c r="G71" t="n">
-        <v>219.16</v>
+        <v>222.35</v>
       </c>
       <c r="H71" t="n">
         <v>1136.57</v>
@@ -70289,7 +70289,7 @@
         <v>1174.31</v>
       </c>
       <c r="G72" t="n">
-        <v>283.51</v>
+        <v>266.81</v>
       </c>
       <c r="H72" t="n">
         <v>1059.28</v>
@@ -70322,7 +70322,7 @@
         <v>1413.42</v>
       </c>
       <c r="G73" t="n">
-        <v>240.17</v>
+        <v>249.09</v>
       </c>
       <c r="H73" t="n">
         <v>1560.25</v>
@@ -70355,7 +70355,7 @@
         <v>3808.64</v>
       </c>
       <c r="G74" t="n">
-        <v>259.16</v>
+        <v>248.72</v>
       </c>
       <c r="H74" t="n">
         <v>2323.88</v>
@@ -70388,7 +70388,7 @@
         <v>4182.56</v>
       </c>
       <c r="G75" t="n">
-        <v>226.72</v>
+        <v>264.12</v>
       </c>
       <c r="H75" t="n">
         <v>1709.69</v>
@@ -70421,7 +70421,7 @@
         <v>2438.37</v>
       </c>
       <c r="G76" t="n">
-        <v>284.7</v>
+        <v>279.4</v>
       </c>
       <c r="H76" t="n">
         <v>1977.4</v>
@@ -70454,7 +70454,7 @@
         <v>3990.01</v>
       </c>
       <c r="G77" t="n">
-        <v>256.74</v>
+        <v>251.58</v>
       </c>
       <c r="H77" t="n">
         <v>1244.87</v>
@@ -70487,7 +70487,7 @@
         <v>4265.21</v>
       </c>
       <c r="G78" t="n">
-        <v>256.98</v>
+        <v>261.05</v>
       </c>
       <c r="H78" t="n">
         <v>2585.15</v>
@@ -70520,7 +70520,7 @@
         <v>3414.78</v>
       </c>
       <c r="G79" t="n">
-        <v>262.12</v>
+        <v>246.59</v>
       </c>
       <c r="H79" t="n">
         <v>2769.39</v>
@@ -70553,7 +70553,7 @@
         <v>1568.3</v>
       </c>
       <c r="G80" t="n">
-        <v>230.34</v>
+        <v>250.56</v>
       </c>
       <c r="H80" t="n">
         <v>2364.64</v>
@@ -70586,7 +70586,7 @@
         <v>2043.03</v>
       </c>
       <c r="G81" t="n">
-        <v>237.86</v>
+        <v>235.15</v>
       </c>
       <c r="H81" t="n">
         <v>2942.26</v>
@@ -70619,7 +70619,7 @@
         <v>1649.82</v>
       </c>
       <c r="G82" t="n">
-        <v>270.93</v>
+        <v>245.6</v>
       </c>
       <c r="H82" t="n">
         <v>2115.36</v>
@@ -70652,7 +70652,7 @@
         <v>2331.38</v>
       </c>
       <c r="G83" t="n">
-        <v>276.46</v>
+        <v>281.24</v>
       </c>
       <c r="H83" t="n">
         <v>2220.19</v>
@@ -70685,7 +70685,7 @@
         <v>1993.78</v>
       </c>
       <c r="G84" t="n">
-        <v>255.82</v>
+        <v>260.89</v>
       </c>
       <c r="H84" t="n">
         <v>1142.55</v>
@@ -70751,7 +70751,7 @@
         <v>1859.8</v>
       </c>
       <c r="G86" t="n">
-        <v>326.69</v>
+        <v>297.9</v>
       </c>
       <c r="H86" t="n">
         <v>1869.55</v>
@@ -70784,7 +70784,7 @@
         <v>2025.84</v>
       </c>
       <c r="G87" t="n">
-        <v>289.16</v>
+        <v>328.16</v>
       </c>
       <c r="H87" t="n">
         <v>1117.98</v>
@@ -70883,7 +70883,7 @@
         <v>2064.59</v>
       </c>
       <c r="G90" t="n">
-        <v>275.02</v>
+        <v>258.95</v>
       </c>
       <c r="H90" t="n">
         <v>1586.54</v>
@@ -70916,7 +70916,7 @@
         <v>1917.03</v>
       </c>
       <c r="G91" t="n">
-        <v>311.64</v>
+        <v>317.51</v>
       </c>
       <c r="H91" t="n">
         <v>1943.12</v>
@@ -70949,7 +70949,7 @@
         <v>2888.13</v>
       </c>
       <c r="G92" t="n">
-        <v>272.38</v>
+        <v>282.72</v>
       </c>
       <c r="H92" t="n">
         <v>1376.91</v>
@@ -70982,7 +70982,7 @@
         <v>3772.89</v>
       </c>
       <c r="G93" t="n">
-        <v>271.78</v>
+        <v>285.24</v>
       </c>
       <c r="H93" t="n">
         <v>2101.52</v>
@@ -71015,7 +71015,7 @@
         <v>5139.53</v>
       </c>
       <c r="G94" t="n">
-        <v>281.29</v>
+        <v>265.03</v>
       </c>
       <c r="H94" t="n">
         <v>1659.23</v>
@@ -71048,7 +71048,7 @@
         <v>5114.29</v>
       </c>
       <c r="G95" t="n">
-        <v>232.53</v>
+        <v>237.95</v>
       </c>
       <c r="H95" t="n">
         <v>1330.92</v>
@@ -71081,7 +71081,7 @@
         <v>2989.67</v>
       </c>
       <c r="G96" t="n">
-        <v>227.93</v>
+        <v>216.76</v>
       </c>
       <c r="H96" t="n">
         <v>2048.96</v>
@@ -71114,7 +71114,7 @@
         <v>3257.53</v>
       </c>
       <c r="G97" t="n">
-        <v>229.02</v>
+        <v>223.75</v>
       </c>
       <c r="H97" t="n">
         <v>1183.69</v>
@@ -71147,7 +71147,7 @@
         <v>1993.09</v>
       </c>
       <c r="G98" t="n">
-        <v>261.49</v>
+        <v>255.9</v>
       </c>
       <c r="H98" t="n">
         <v>602.79</v>
@@ -71180,7 +71180,7 @@
         <v>1950.78</v>
       </c>
       <c r="G99" t="n">
-        <v>247.96</v>
+        <v>279.93</v>
       </c>
       <c r="H99" t="n">
         <v>635.16</v>
@@ -71213,7 +71213,7 @@
         <v>1107.86</v>
       </c>
       <c r="G100" t="n">
-        <v>272.17</v>
+        <v>267.36</v>
       </c>
       <c r="H100" t="n">
         <v>692.9400000000001</v>
@@ -71246,7 +71246,7 @@
         <v>1859.55</v>
       </c>
       <c r="G101" t="n">
-        <v>264.32</v>
+        <v>236.18</v>
       </c>
       <c r="H101" t="n">
         <v>392.96</v>
@@ -71279,7 +71279,7 @@
         <v>1722.21</v>
       </c>
       <c r="G102" t="n">
-        <v>263.42</v>
+        <v>266.44</v>
       </c>
       <c r="H102" t="n">
         <v>1128.28</v>
@@ -71312,7 +71312,7 @@
         <v>2233.44</v>
       </c>
       <c r="G103" t="n">
-        <v>250.6</v>
+        <v>260.72</v>
       </c>
       <c r="H103" t="n">
         <v>409.3</v>
@@ -71345,7 +71345,7 @@
         <v>2754.91</v>
       </c>
       <c r="G104" t="n">
-        <v>246.3</v>
+        <v>257.88</v>
       </c>
       <c r="H104" t="n">
         <v>2542.11</v>
@@ -71378,7 +71378,7 @@
         <v>2904.56</v>
       </c>
       <c r="G105" t="n">
-        <v>256.98</v>
+        <v>269.19</v>
       </c>
       <c r="H105" t="n">
         <v>5005.32</v>
@@ -71411,7 +71411,7 @@
         <v>2097.87</v>
       </c>
       <c r="G106" t="n">
-        <v>267.56</v>
+        <v>262.74</v>
       </c>
       <c r="H106" t="n">
         <v>2450.52</v>
@@ -71444,7 +71444,7 @@
         <v>2904.69</v>
       </c>
       <c r="G107" t="n">
-        <v>237.57</v>
+        <v>229.52</v>
       </c>
       <c r="H107" t="n">
         <v>3536.1</v>
@@ -71477,7 +71477,7 @@
         <v>2462.16</v>
       </c>
       <c r="G108" t="n">
-        <v>266.64</v>
+        <v>279.97</v>
       </c>
       <c r="H108" t="n">
         <v>1410.69</v>
@@ -71510,7 +71510,7 @@
         <v>2542.49</v>
       </c>
       <c r="G109" t="n">
-        <v>269.3</v>
+        <v>249.5</v>
       </c>
       <c r="H109" t="n">
         <v>3993.16</v>
@@ -71543,7 +71543,7 @@
         <v>1467.5</v>
       </c>
       <c r="G110" t="n">
-        <v>268.1</v>
+        <v>251.07</v>
       </c>
       <c r="H110" t="n">
         <v>2328.29</v>
@@ -71576,7 +71576,7 @@
         <v>1689.03</v>
       </c>
       <c r="G111" t="n">
-        <v>257.37</v>
+        <v>266.2</v>
       </c>
       <c r="H111" t="n">
         <v>1635.46</v>
@@ -71609,7 +71609,7 @@
         <v>1660.18</v>
       </c>
       <c r="G112" t="n">
-        <v>255.37</v>
+        <v>271.98</v>
       </c>
       <c r="H112" t="n">
         <v>1168.02</v>
@@ -71642,7 +71642,7 @@
         <v>1687.64</v>
       </c>
       <c r="G113" t="n">
-        <v>240.87</v>
+        <v>233.44</v>
       </c>
       <c r="H113" t="n">
         <v>2700.38</v>
@@ -71675,7 +71675,7 @@
         <v>1679.82</v>
       </c>
       <c r="G114" t="n">
-        <v>267.5</v>
+        <v>271.25</v>
       </c>
       <c r="H114" t="n">
         <v>1168.17</v>
@@ -71708,7 +71708,7 @@
         <v>1620.1</v>
       </c>
       <c r="G115" t="n">
-        <v>241.01</v>
+        <v>237.28</v>
       </c>
       <c r="H115" t="n">
         <v>2722.94</v>
@@ -71741,7 +71741,7 @@
         <v>2580.61</v>
       </c>
       <c r="G116" t="n">
-        <v>265.07</v>
+        <v>270.08</v>
       </c>
       <c r="H116" t="n">
         <v>1567.46</v>
@@ -71774,7 +71774,7 @@
         <v>1987.89</v>
       </c>
       <c r="G117" t="n">
-        <v>239.03</v>
+        <v>253.23</v>
       </c>
       <c r="H117" t="n">
         <v>2208.67</v>
@@ -71873,7 +71873,7 @@
         <v>2155.12</v>
       </c>
       <c r="G120" t="n">
-        <v>267.11</v>
+        <v>253.69</v>
       </c>
       <c r="H120" t="n">
         <v>2693</v>
@@ -71906,7 +71906,7 @@
         <v>2198.14</v>
       </c>
       <c r="G121" t="n">
-        <v>228.44</v>
+        <v>221.33</v>
       </c>
       <c r="H121" t="n">
         <v>2607.38</v>
@@ -71939,7 +71939,7 @@
         <v>1127.51</v>
       </c>
       <c r="G122" t="n">
-        <v>258.98</v>
+        <v>253.08</v>
       </c>
       <c r="H122" t="n">
         <v>1143.7</v>
@@ -71972,7 +71972,7 @@
         <v>1253.95</v>
       </c>
       <c r="G123" t="n">
-        <v>259.59</v>
+        <v>263.84</v>
       </c>
       <c r="H123" t="n">
         <v>1734.89</v>
@@ -72005,7 +72005,7 @@
         <v>1792.27</v>
       </c>
       <c r="G124" t="n">
-        <v>258.48</v>
+        <v>271.97</v>
       </c>
       <c r="H124" t="n">
         <v>1000.12</v>
@@ -72104,7 +72104,7 @@
         <v>1393.18</v>
       </c>
       <c r="G127" t="n">
-        <v>250.94</v>
+        <v>239.19</v>
       </c>
       <c r="H127" t="n">
         <v>757.92</v>
@@ -72137,7 +72137,7 @@
         <v>2005.59</v>
       </c>
       <c r="G128" t="n">
-        <v>270.01</v>
+        <v>258.34</v>
       </c>
       <c r="H128" t="n">
         <v>1815.64</v>
@@ -72170,7 +72170,7 @@
         <v>1750.01</v>
       </c>
       <c r="G129" t="n">
-        <v>248.38</v>
+        <v>280.64</v>
       </c>
       <c r="H129" t="n">
         <v>1916.27</v>
@@ -72269,7 +72269,7 @@
         <v>1596.54</v>
       </c>
       <c r="G132" t="n">
-        <v>245.6</v>
+        <v>238.59</v>
       </c>
       <c r="H132" t="n">
         <v>1612.14</v>
@@ -72302,7 +72302,7 @@
         <v>1829.67</v>
       </c>
       <c r="G133" t="n">
-        <v>241.01</v>
+        <v>233.55</v>
       </c>
       <c r="H133" t="n">
         <v>1756.85</v>
@@ -72335,7 +72335,7 @@
         <v>2724.52</v>
       </c>
       <c r="G134" t="n">
-        <v>260.49</v>
+        <v>272.59</v>
       </c>
       <c r="H134" t="n">
         <v>834.39</v>
@@ -72368,7 +72368,7 @@
         <v>1307.67</v>
       </c>
       <c r="G135" t="n">
-        <v>223.31</v>
+        <v>234.97</v>
       </c>
       <c r="H135" t="n">
         <v>555.4400000000001</v>
@@ -72401,7 +72401,7 @@
         <v>2613.2</v>
       </c>
       <c r="G136" t="n">
-        <v>267.08</v>
+        <v>262.29</v>
       </c>
       <c r="H136" t="n">
         <v>1105.94</v>
@@ -72434,7 +72434,7 @@
         <v>2710.87</v>
       </c>
       <c r="G137" t="n">
-        <v>284.83</v>
+        <v>263.63</v>
       </c>
       <c r="H137" t="n">
         <v>463.69</v>
@@ -72467,7 +72467,7 @@
         <v>2004.75</v>
       </c>
       <c r="G138" t="n">
-        <v>230.55</v>
+        <v>228</v>
       </c>
       <c r="H138" t="n">
         <v>389.54</v>
@@ -72500,7 +72500,7 @@
         <v>2659.87</v>
       </c>
       <c r="G139" t="n">
-        <v>237.51</v>
+        <v>232.82</v>
       </c>
       <c r="H139" t="n">
         <v>819.4299999999999</v>
@@ -72533,7 +72533,7 @@
         <v>2173.22</v>
       </c>
       <c r="G140" t="n">
-        <v>271.39</v>
+        <v>277.34</v>
       </c>
       <c r="H140" t="n">
         <v>3305.32</v>
@@ -72566,7 +72566,7 @@
         <v>2079.63</v>
       </c>
       <c r="G141" t="n">
-        <v>261.86</v>
+        <v>265.73</v>
       </c>
       <c r="H141" t="n">
         <v>1505.06</v>
@@ -72599,7 +72599,7 @@
         <v>1663.42</v>
       </c>
       <c r="G142" t="n">
-        <v>267.5</v>
+        <v>261.88</v>
       </c>
       <c r="H142" t="n">
         <v>964.85</v>
@@ -72632,7 +72632,7 @@
         <v>2017.15</v>
       </c>
       <c r="G143" t="n">
-        <v>278.74</v>
+        <v>283.66</v>
       </c>
       <c r="H143" t="n">
         <v>3294.86</v>
@@ -72698,7 +72698,7 @@
         <v>2414.56</v>
       </c>
       <c r="G145" t="n">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="H145" t="n">
         <v>2459.16</v>
@@ -72764,7 +72764,7 @@
         <v>1487.45</v>
       </c>
       <c r="G147" t="n">
-        <v>220.91</v>
+        <v>233.46</v>
       </c>
       <c r="H147" t="n">
         <v>2226.63</v>
@@ -72797,7 +72797,7 @@
         <v>1072.47</v>
       </c>
       <c r="G148" t="n">
-        <v>316.07</v>
+        <v>349.23</v>
       </c>
       <c r="H148" t="n">
         <v>2049.53</v>
@@ -72830,7 +72830,7 @@
         <v>1196.26</v>
       </c>
       <c r="G149" t="n">
-        <v>293.81</v>
+        <v>288.88</v>
       </c>
       <c r="H149" t="n">
         <v>1248.15</v>
@@ -72863,7 +72863,7 @@
         <v>1017.6</v>
       </c>
       <c r="G150" t="n">
-        <v>266.16</v>
+        <v>249.62</v>
       </c>
       <c r="H150" t="n">
         <v>832.92</v>
@@ -72896,7 +72896,7 @@
         <v>1816.08</v>
       </c>
       <c r="G151" t="n">
-        <v>261.99</v>
+        <v>244.28</v>
       </c>
       <c r="H151" t="n">
         <v>1521.8</v>
@@ -72929,7 +72929,7 @@
         <v>1395.23</v>
       </c>
       <c r="G152" t="n">
-        <v>275.56</v>
+        <v>253.34</v>
       </c>
       <c r="H152" t="n">
         <v>1730.29</v>
@@ -72962,7 +72962,7 @@
         <v>1939.84</v>
       </c>
       <c r="G153" t="n">
-        <v>243.95</v>
+        <v>259.93</v>
       </c>
       <c r="H153" t="n">
         <v>1054.65</v>
@@ -72995,7 +72995,7 @@
         <v>2095.01</v>
       </c>
       <c r="G154" t="n">
-        <v>235.71</v>
+        <v>243.65</v>
       </c>
       <c r="H154" t="n">
         <v>1619.77</v>
@@ -73094,7 +73094,7 @@
         <v>1403.91</v>
       </c>
       <c r="G157" t="n">
-        <v>243.6</v>
+        <v>239.64</v>
       </c>
       <c r="H157" t="n">
         <v>1194.53</v>
@@ -73127,7 +73127,7 @@
         <v>1932.47</v>
       </c>
       <c r="G158" t="n">
-        <v>241.01</v>
+        <v>244.17</v>
       </c>
       <c r="H158" t="n">
         <v>3716.15</v>
@@ -73160,7 +73160,7 @@
         <v>3003.43</v>
       </c>
       <c r="G159" t="n">
-        <v>282.11</v>
+        <v>304.01</v>
       </c>
       <c r="H159" t="n">
         <v>4782.3</v>
@@ -73193,7 +73193,7 @@
         <v>2284.94</v>
       </c>
       <c r="G160" t="n">
-        <v>274.13</v>
+        <v>258.25</v>
       </c>
       <c r="H160" t="n">
         <v>1929.06</v>
@@ -73226,7 +73226,7 @@
         <v>2589.86</v>
       </c>
       <c r="G161" t="n">
-        <v>240.12</v>
+        <v>236.47</v>
       </c>
       <c r="H161" t="n">
         <v>4101.89</v>
@@ -73259,7 +73259,7 @@
         <v>3162.67</v>
       </c>
       <c r="G162" t="n">
-        <v>255.46</v>
+        <v>245.37</v>
       </c>
       <c r="H162" t="n">
         <v>4356.25</v>
@@ -73292,7 +73292,7 @@
         <v>1689.14</v>
       </c>
       <c r="G163" t="n">
-        <v>260.19</v>
+        <v>265.66</v>
       </c>
       <c r="H163" t="n">
         <v>3212.04</v>
@@ -73325,7 +73325,7 @@
         <v>3482.99</v>
       </c>
       <c r="G164" t="n">
-        <v>270.08</v>
+        <v>266.57</v>
       </c>
       <c r="H164" t="n">
         <v>2993.61</v>
@@ -73358,7 +73358,7 @@
         <v>3554.78</v>
       </c>
       <c r="G165" t="n">
-        <v>249.61</v>
+        <v>282.68</v>
       </c>
       <c r="H165" t="n">
         <v>3122.51</v>
@@ -73391,7 +73391,7 @@
         <v>2121.9</v>
       </c>
       <c r="G166" t="n">
-        <v>230.28</v>
+        <v>227.53</v>
       </c>
       <c r="H166" t="n">
         <v>1732.53</v>
@@ -73424,7 +73424,7 @@
         <v>2899.81</v>
       </c>
       <c r="G167" t="n">
-        <v>278.48</v>
+        <v>268.01</v>
       </c>
       <c r="H167" t="n">
         <v>1797.89</v>
@@ -73457,7 +73457,7 @@
         <v>2344.99</v>
       </c>
       <c r="G168" t="n">
-        <v>252.52</v>
+        <v>238.51</v>
       </c>
       <c r="H168" t="n">
         <v>2903.82</v>
@@ -73490,7 +73490,7 @@
         <v>4043.17</v>
       </c>
       <c r="G169" t="n">
-        <v>262.6</v>
+        <v>273.99</v>
       </c>
       <c r="H169" t="n">
         <v>1685.29</v>
@@ -73556,7 +73556,7 @@
         <v>2938.45</v>
       </c>
       <c r="G171" t="n">
-        <v>255.26</v>
+        <v>266.31</v>
       </c>
       <c r="H171" t="n">
         <v>493.51</v>
@@ -73589,7 +73589,7 @@
         <v>3608.56</v>
       </c>
       <c r="G172" t="n">
-        <v>246.76</v>
+        <v>243.84</v>
       </c>
       <c r="H172" t="n">
         <v>342.9</v>
@@ -73622,7 +73622,7 @@
         <v>2561.53</v>
       </c>
       <c r="G173" t="n">
-        <v>296.66</v>
+        <v>277.33</v>
       </c>
       <c r="H173" t="n">
         <v>323.14</v>
@@ -73688,7 +73688,7 @@
         <v>4923.71</v>
       </c>
       <c r="G175" t="n">
-        <v>220.37</v>
+        <v>227.16</v>
       </c>
       <c r="H175" t="n">
         <v>626.73</v>
@@ -73754,7 +73754,7 @@
         <v>2750.36</v>
       </c>
       <c r="G177" t="n">
-        <v>238.45</v>
+        <v>256.2</v>
       </c>
       <c r="H177" t="n">
         <v>1421.87</v>
@@ -73787,7 +73787,7 @@
         <v>1745.32</v>
       </c>
       <c r="G178" t="n">
-        <v>252.77</v>
+        <v>257.17</v>
       </c>
       <c r="H178" t="n">
         <v>1502.42</v>
@@ -73820,7 +73820,7 @@
         <v>1891.54</v>
       </c>
       <c r="G179" t="n">
-        <v>252.83</v>
+        <v>230.82</v>
       </c>
       <c r="H179" t="n">
         <v>2744.65</v>
@@ -73853,7 +73853,7 @@
         <v>2179.58</v>
       </c>
       <c r="G180" t="n">
-        <v>238</v>
+        <v>229.86</v>
       </c>
       <c r="H180" t="n">
         <v>1929.42</v>
@@ -73886,7 +73886,7 @@
         <v>2932.98</v>
       </c>
       <c r="G181" t="n">
-        <v>241.39</v>
+        <v>244.15</v>
       </c>
       <c r="H181" t="n">
         <v>1885.67</v>
@@ -73919,7 +73919,7 @@
         <v>1374.43</v>
       </c>
       <c r="G182" t="n">
-        <v>247.58</v>
+        <v>239.65</v>
       </c>
       <c r="H182" t="n">
         <v>579.58</v>
@@ -73952,7 +73952,7 @@
         <v>1554.56</v>
       </c>
       <c r="G183" t="n">
-        <v>255.58</v>
+        <v>272.69</v>
       </c>
       <c r="H183" t="n">
         <v>1350.9</v>
@@ -73985,7 +73985,7 @@
         <v>1158.82</v>
       </c>
       <c r="G184" t="n">
-        <v>236.96</v>
+        <v>242.64</v>
       </c>
       <c r="H184" t="n">
         <v>1102.66</v>
@@ -74018,7 +74018,7 @@
         <v>1394.24</v>
       </c>
       <c r="G185" t="n">
-        <v>289.8</v>
+        <v>263.39</v>
       </c>
       <c r="H185" t="n">
         <v>921.4299999999999</v>
@@ -74051,7 +74051,7 @@
         <v>916.0599999999999</v>
       </c>
       <c r="G186" t="n">
-        <v>279.2</v>
+        <v>273.55</v>
       </c>
       <c r="H186" t="n">
         <v>579.64</v>
@@ -74084,7 +74084,7 @@
         <v>1249.28</v>
       </c>
       <c r="G187" t="n">
-        <v>220.24</v>
+        <v>225.3</v>
       </c>
       <c r="H187" t="n">
         <v>1615.51</v>
@@ -74150,7 +74150,7 @@
         <v>2310.17</v>
       </c>
       <c r="G189" t="n">
-        <v>249.32</v>
+        <v>260.7</v>
       </c>
       <c r="H189" t="n">
         <v>1630.28</v>
@@ -74183,7 +74183,7 @@
         <v>2041.9</v>
       </c>
       <c r="G190" t="n">
-        <v>289.9</v>
+        <v>275.7</v>
       </c>
       <c r="H190" t="n">
         <v>1622.62</v>
@@ -74216,7 +74216,7 @@
         <v>1605.75</v>
       </c>
       <c r="G191" t="n">
-        <v>288.8</v>
+        <v>294.72</v>
       </c>
       <c r="H191" t="n">
         <v>945.38</v>
@@ -74282,7 +74282,7 @@
         <v>2849.04</v>
       </c>
       <c r="G193" t="n">
-        <v>258.7</v>
+        <v>254.51</v>
       </c>
       <c r="H193" t="n">
         <v>2763.84</v>
@@ -74315,7 +74315,7 @@
         <v>3435.63</v>
       </c>
       <c r="G194" t="n">
-        <v>256.85</v>
+        <v>245.48</v>
       </c>
       <c r="H194" t="n">
         <v>1670.71</v>
@@ -74348,7 +74348,7 @@
         <v>3045.91</v>
       </c>
       <c r="G195" t="n">
-        <v>271.11</v>
+        <v>287.51</v>
       </c>
       <c r="H195" t="n">
         <v>3044.52</v>
@@ -74381,7 +74381,7 @@
         <v>3184.82</v>
       </c>
       <c r="G196" t="n">
-        <v>280.62</v>
+        <v>269.87</v>
       </c>
       <c r="H196" t="n">
         <v>2635.29</v>
@@ -74414,7 +74414,7 @@
         <v>2433.07</v>
       </c>
       <c r="G197" t="n">
-        <v>228.56</v>
+        <v>235.69</v>
       </c>
       <c r="H197" t="n">
         <v>1223.06</v>
@@ -74447,7 +74447,7 @@
         <v>2786.37</v>
       </c>
       <c r="G198" t="n">
-        <v>248.39</v>
+        <v>244.67</v>
       </c>
       <c r="H198" t="n">
         <v>3396.49</v>
@@ -74480,7 +74480,7 @@
         <v>4360.45</v>
       </c>
       <c r="G199" t="n">
-        <v>219.61</v>
+        <v>222.42</v>
       </c>
       <c r="H199" t="n">
         <v>3018.17</v>
@@ -74513,7 +74513,7 @@
         <v>3200.82</v>
       </c>
       <c r="G200" t="n">
-        <v>255.32</v>
+        <v>250.29</v>
       </c>
       <c r="H200" t="n">
         <v>1359.76</v>
@@ -74546,7 +74546,7 @@
         <v>4608.17</v>
       </c>
       <c r="G201" t="n">
-        <v>311.89</v>
+        <v>341.33</v>
       </c>
       <c r="H201" t="n">
         <v>596.1799999999999</v>
@@ -74579,7 +74579,7 @@
         <v>3401.04</v>
       </c>
       <c r="G202" t="n">
-        <v>242.6</v>
+        <v>258.99</v>
       </c>
       <c r="H202" t="n">
         <v>602.38</v>
@@ -74612,7 +74612,7 @@
         <v>3105.89</v>
       </c>
       <c r="G203" t="n">
-        <v>240.61</v>
+        <v>233.84</v>
       </c>
       <c r="H203" t="n">
         <v>566.48</v>
@@ -74645,7 +74645,7 @@
         <v>2747.63</v>
       </c>
       <c r="G204" t="n">
-        <v>270.68</v>
+        <v>242.41</v>
       </c>
       <c r="H204" t="n">
         <v>1204.08</v>
@@ -74678,7 +74678,7 @@
         <v>3469.11</v>
       </c>
       <c r="G205" t="n">
-        <v>280.97</v>
+        <v>276.2</v>
       </c>
       <c r="H205" t="n">
         <v>339.23</v>
@@ -74711,7 +74711,7 @@
         <v>1735.74</v>
       </c>
       <c r="G206" t="n">
-        <v>304.31</v>
+        <v>319.95</v>
       </c>
       <c r="H206" t="n">
         <v>2617.68</v>
@@ -74744,7 +74744,7 @@
         <v>1355.53</v>
       </c>
       <c r="G207" t="n">
-        <v>245.85</v>
+        <v>264.95</v>
       </c>
       <c r="H207" t="n">
         <v>1742.84</v>
@@ -74777,7 +74777,7 @@
         <v>1207.86</v>
       </c>
       <c r="G208" t="n">
-        <v>285.63</v>
+        <v>297.05</v>
       </c>
       <c r="H208" t="n">
         <v>2070.34</v>
@@ -74843,7 +74843,7 @@
         <v>1222.41</v>
       </c>
       <c r="G210" t="n">
-        <v>260.35</v>
+        <v>240.23</v>
       </c>
       <c r="H210" t="n">
         <v>2073.35</v>
@@ -74876,7 +74876,7 @@
         <v>1978.52</v>
       </c>
       <c r="G211" t="n">
-        <v>339.31</v>
+        <v>305.88</v>
       </c>
       <c r="H211" t="n">
         <v>1852.77</v>
@@ -74909,7 +74909,7 @@
         <v>1782.55</v>
       </c>
       <c r="G212" t="n">
-        <v>304.6</v>
+        <v>310.41</v>
       </c>
       <c r="H212" t="n">
         <v>1334.84</v>
@@ -74942,7 +74942,7 @@
         <v>1251.21</v>
       </c>
       <c r="G213" t="n">
-        <v>238.41</v>
+        <v>242.25</v>
       </c>
       <c r="H213" t="n">
         <v>623.78</v>
@@ -74975,7 +74975,7 @@
         <v>2099.4</v>
       </c>
       <c r="G214" t="n">
-        <v>275.01</v>
+        <v>269.24</v>
       </c>
       <c r="H214" t="n">
         <v>1250.92</v>
@@ -75008,7 +75008,7 @@
         <v>1619.18</v>
       </c>
       <c r="G215" t="n">
-        <v>247.86</v>
+        <v>253.84</v>
       </c>
       <c r="H215" t="n">
         <v>2175.81</v>
@@ -75041,7 +75041,7 @@
         <v>1629.6</v>
       </c>
       <c r="G216" t="n">
-        <v>288.38</v>
+        <v>293.58</v>
       </c>
       <c r="H216" t="n">
         <v>936.08</v>
@@ -75074,7 +75074,7 @@
         <v>1408.84</v>
       </c>
       <c r="G217" t="n">
-        <v>248.37</v>
+        <v>238.7</v>
       </c>
       <c r="H217" t="n">
         <v>1532.74</v>
@@ -75107,7 +75107,7 @@
         <v>2419.84</v>
       </c>
       <c r="G218" t="n">
-        <v>284.52</v>
+        <v>288.97</v>
       </c>
       <c r="H218" t="n">
         <v>1192.88</v>
@@ -75140,7 +75140,7 @@
         <v>2474.71</v>
       </c>
       <c r="G219" t="n">
-        <v>239.61</v>
+        <v>243.21</v>
       </c>
       <c r="H219" t="n">
         <v>2407.54</v>
@@ -75206,7 +75206,7 @@
         <v>3113.17</v>
       </c>
       <c r="G221" t="n">
-        <v>265.5</v>
+        <v>251.47</v>
       </c>
       <c r="H221" t="n">
         <v>2846.52</v>
@@ -75239,7 +75239,7 @@
         <v>2286.35</v>
       </c>
       <c r="G222" t="n">
-        <v>238.95</v>
+        <v>235.05</v>
       </c>
       <c r="H222" t="n">
         <v>1455.34</v>
@@ -75272,7 +75272,7 @@
         <v>2644.4</v>
       </c>
       <c r="G223" t="n">
-        <v>224.36</v>
+        <v>231.33</v>
       </c>
       <c r="H223" t="n">
         <v>1937.03</v>
@@ -75338,7 +75338,7 @@
         <v>1893.69</v>
       </c>
       <c r="G225" t="n">
-        <v>240.23</v>
+        <v>246.94</v>
       </c>
       <c r="H225" t="n">
         <v>2460.6</v>
@@ -75371,7 +75371,7 @@
         <v>1829.95</v>
       </c>
       <c r="G226" t="n">
-        <v>241.25</v>
+        <v>237.81</v>
       </c>
       <c r="H226" t="n">
         <v>2013.52</v>
@@ -75437,7 +75437,7 @@
         <v>1495.49</v>
       </c>
       <c r="G228" t="n">
-        <v>233.78</v>
+        <v>230.97</v>
       </c>
       <c r="H228" t="n">
         <v>1382.13</v>
@@ -75503,7 +75503,7 @@
         <v>1884.08</v>
       </c>
       <c r="G230" t="n">
-        <v>276.12</v>
+        <v>270.68</v>
       </c>
       <c r="H230" t="n">
         <v>3627.3</v>
@@ -75569,7 +75569,7 @@
         <v>2813.05</v>
       </c>
       <c r="G232" t="n">
-        <v>264.03</v>
+        <v>268.95</v>
       </c>
       <c r="H232" t="n">
         <v>2097.76</v>
@@ -75602,7 +75602,7 @@
         <v>1582.05</v>
       </c>
       <c r="G233" t="n">
-        <v>244.36</v>
+        <v>254.22</v>
       </c>
       <c r="H233" t="n">
         <v>1767.51</v>
@@ -75635,7 +75635,7 @@
         <v>1689.4</v>
       </c>
       <c r="G234" t="n">
-        <v>257.57</v>
+        <v>260.45</v>
       </c>
       <c r="H234" t="n">
         <v>1769.79</v>
@@ -75668,7 +75668,7 @@
         <v>1683.36</v>
       </c>
       <c r="G235" t="n">
-        <v>251.78</v>
+        <v>243.61</v>
       </c>
       <c r="H235" t="n">
         <v>1273.44</v>
@@ -75734,7 +75734,7 @@
         <v>1495.53</v>
       </c>
       <c r="G237" t="n">
-        <v>241.97</v>
+        <v>255.96</v>
       </c>
       <c r="H237" t="n">
         <v>2257.08</v>
@@ -75767,7 +75767,7 @@
         <v>2077.1</v>
       </c>
       <c r="G238" t="n">
-        <v>262.86</v>
+        <v>258.02</v>
       </c>
       <c r="H238" t="n">
         <v>1564.09</v>
@@ -75833,7 +75833,7 @@
         <v>2241.08</v>
       </c>
       <c r="G240" t="n">
-        <v>259.58</v>
+        <v>248.75</v>
       </c>
       <c r="H240" t="n">
         <v>2746.38</v>
@@ -75899,7 +75899,7 @@
         <v>2536.71</v>
       </c>
       <c r="G242" t="n">
-        <v>233.35</v>
+        <v>236.69</v>
       </c>
       <c r="H242" t="n">
         <v>2190.42</v>
@@ -75932,7 +75932,7 @@
         <v>2241.64</v>
       </c>
       <c r="G243" t="n">
-        <v>292.44</v>
+        <v>278.58</v>
       </c>
       <c r="H243" t="n">
         <v>4945.83</v>
@@ -75965,7 +75965,7 @@
         <v>2684.85</v>
       </c>
       <c r="G244" t="n">
-        <v>227.73</v>
+        <v>236.97</v>
       </c>
       <c r="H244" t="n">
         <v>4024.05</v>
@@ -75998,7 +75998,7 @@
         <v>3469.72</v>
       </c>
       <c r="G245" t="n">
-        <v>328.76</v>
+        <v>317.05</v>
       </c>
       <c r="H245" t="n">
         <v>2328.42</v>
@@ -76031,7 +76031,7 @@
         <v>2591.58</v>
       </c>
       <c r="G246" t="n">
-        <v>224.62</v>
+        <v>221.1</v>
       </c>
       <c r="H246" t="n">
         <v>5068.84</v>
@@ -76064,7 +76064,7 @@
         <v>2020.37</v>
       </c>
       <c r="G247" t="n">
-        <v>253.74</v>
+        <v>265.68</v>
       </c>
       <c r="H247" t="n">
         <v>5009.02</v>
@@ -76097,7 +76097,7 @@
         <v>2008.98</v>
       </c>
       <c r="G248" t="n">
-        <v>289.04</v>
+        <v>293.72</v>
       </c>
       <c r="H248" t="n">
         <v>1900.7</v>
@@ -76130,7 +76130,7 @@
         <v>1960.02</v>
       </c>
       <c r="G249" t="n">
-        <v>246.27</v>
+        <v>278.66</v>
       </c>
       <c r="H249" t="n">
         <v>1086.81</v>
@@ -76163,7 +76163,7 @@
         <v>1808.79</v>
       </c>
       <c r="G250" t="n">
-        <v>276.8</v>
+        <v>264.68</v>
       </c>
       <c r="H250" t="n">
         <v>2324.05</v>
@@ -76196,7 +76196,7 @@
         <v>1583.19</v>
       </c>
       <c r="G251" t="n">
-        <v>233.94</v>
+        <v>228.72</v>
       </c>
       <c r="H251" t="n">
         <v>2507.99</v>
@@ -76229,7 +76229,7 @@
         <v>2286.1</v>
       </c>
       <c r="G252" t="n">
-        <v>265.1</v>
+        <v>259.67</v>
       </c>
       <c r="H252" t="n">
         <v>1669.46</v>
@@ -76262,7 +76262,7 @@
         <v>2192.89</v>
       </c>
       <c r="G253" t="n">
-        <v>245.04</v>
+        <v>237.53</v>
       </c>
       <c r="H253" t="n">
         <v>2743.66</v>
